--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output3.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X191"/>
+  <dimension ref="A1:Y191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,45 +498,50 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>AssetID_9343_smooth</t>
+          <t>AssetID_9368_smooth</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>AssetID_12208_smooth</t>
+          <t>AssetID_9369_smooth</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>AssetID_9370_smooth</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>AssetID_9358_smooth</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>AssetID_9359_smooth</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>AssetID_9360_smooth</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>AssetID_9361_smooth</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Behavior_Cluster</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Degradation_Index</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Health_Status</t>
         </is>
@@ -591,30 +596,33 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>97.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.04</v>
+        <v>71</v>
       </c>
       <c r="R2" t="n">
+        <v>74</v>
+      </c>
+      <c r="S2" t="n">
         <v>33.2</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>38.2</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>31.2</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>51.8</v>
       </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="W2" t="n">
-        <v>0.9966356936626155</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9819015806106599</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -669,30 +677,33 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.56</v>
+        <v>71</v>
       </c>
       <c r="R3" t="n">
+        <v>74</v>
+      </c>
+      <c r="S3" t="n">
         <v>33.4</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>38</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>31</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>51.8</v>
       </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.004369869610255</v>
-      </c>
-      <c r="X3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9800403146429144</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -747,30 +758,33 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.86</v>
+        <v>71</v>
       </c>
       <c r="R4" t="n">
+        <v>74</v>
+      </c>
+      <c r="S4" t="n">
         <v>33.2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>38.4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>52</v>
       </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.03462558582863</v>
-      </c>
-      <c r="X4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9851266787052438</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -825,30 +839,33 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.8</v>
+        <v>71</v>
       </c>
       <c r="R5" t="n">
+        <v>74</v>
+      </c>
+      <c r="S5" t="n">
         <v>33.2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>39</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>30.2</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>51.8</v>
       </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.066647968881647</v>
-      </c>
-      <c r="X5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.013141218972463</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -903,30 +920,33 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>93.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.64</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
+        <v>74</v>
+      </c>
+      <c r="S6" t="n">
         <v>33.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>39.2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>29.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>50.4</v>
       </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="W6" t="n">
-        <v>0.9987248545396611</v>
-      </c>
-      <c r="X6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06317105454265</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -981,30 +1001,33 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.74</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
+        <v>74</v>
+      </c>
+      <c r="S7" t="n">
         <v>33</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>39.8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>29.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>49.6</v>
       </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.023994606653538</v>
-      </c>
-      <c r="X7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.220788314266936</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1059,30 +1082,33 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.92</v>
+        <v>71</v>
       </c>
       <c r="R8" t="n">
+        <v>74</v>
+      </c>
+      <c r="S8" t="n">
         <v>32.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>39.8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>30.2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>49.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.022394160214932</v>
-      </c>
-      <c r="X8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.095746168349207</v>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1137,30 +1163,33 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.64</v>
+        <v>71</v>
       </c>
       <c r="R9" t="n">
+        <v>74</v>
+      </c>
+      <c r="S9" t="n">
         <v>32</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>39.8</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>30.6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>50.2</v>
       </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.004310395790712</v>
-      </c>
-      <c r="X9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08298495941274</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1215,30 +1244,33 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.64</v>
+        <v>71</v>
       </c>
       <c r="R10" t="n">
+        <v>74</v>
+      </c>
+      <c r="S10" t="n">
         <v>31.6</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>39.6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>31</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>51</v>
       </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
       <c r="W10" t="n">
-        <v>0.992640985065934</v>
-      </c>
-      <c r="X10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.081875147632436</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1293,32 +1325,35 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.22</v>
+        <v>71</v>
       </c>
       <c r="R11" t="n">
+        <v>74</v>
+      </c>
+      <c r="S11" t="n">
         <v>31.2</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>40</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>31.2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>52</v>
       </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.005139996680721</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.319838949760902</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -1371,30 +1406,33 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>90.2</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.22</v>
+        <v>71</v>
       </c>
       <c r="R12" t="n">
+        <v>74</v>
+      </c>
+      <c r="S12" t="n">
         <v>32</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>40</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>31.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>52.4</v>
       </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
-        <v>0.9964475540029157</v>
-      </c>
-      <c r="X12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.283507660898609</v>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1449,30 +1487,33 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>90.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.04</v>
+        <v>71</v>
       </c>
       <c r="R13" t="n">
+        <v>74</v>
+      </c>
+      <c r="S13" t="n">
         <v>32.4</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>40</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>30.8</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>51.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
       <c r="W13" t="n">
-        <v>0.9966718884083822</v>
-      </c>
-      <c r="X13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.158584829458703</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1527,30 +1568,33 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>90.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.06</v>
+        <v>71</v>
       </c>
       <c r="R14" t="n">
+        <v>74</v>
+      </c>
+      <c r="S14" t="n">
         <v>32.8</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>39.8</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>30.2</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>50.6</v>
       </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.043730895009383</v>
-      </c>
-      <c r="X14" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06193190470639</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1605,30 +1649,33 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.8</v>
+        <v>71</v>
       </c>
       <c r="R15" t="n">
+        <v>74</v>
+      </c>
+      <c r="S15" t="n">
         <v>32.8</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39.4</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>29.8</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>49.6</v>
       </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.077289098703722</v>
-      </c>
-      <c r="X15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.132353520234631</v>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1683,30 +1730,33 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="n">
-        <v>19.44</v>
+        <v>71</v>
       </c>
       <c r="R16" t="n">
+        <v>74</v>
+      </c>
+      <c r="S16" t="n">
         <v>32.6</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>39</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>30.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>49.8</v>
       </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.002856464570411</v>
-      </c>
-      <c r="X16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.022308203874668</v>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1761,30 +1811,33 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>94.2192</v>
+        <v>76</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.64</v>
+        <v>71</v>
       </c>
       <c r="R17" t="n">
+        <v>74</v>
+      </c>
+      <c r="S17" t="n">
         <v>31.8</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>38.2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>31.2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>50.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
       <c r="W17" t="n">
-        <v>0.9880278008546137</v>
-      </c>
-      <c r="X17" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.139906374584114</v>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1839,30 +1892,33 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>95.61920000000001</v>
+        <v>76</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.04</v>
+        <v>71</v>
       </c>
       <c r="R18" t="n">
+        <v>74</v>
+      </c>
+      <c r="S18" t="n">
         <v>32</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>37.6</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>31.8</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>51.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.007766329631072</v>
-      </c>
-      <c r="X18" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.090400373580606</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1917,30 +1973,33 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>95.4192</v>
+        <v>76</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.34</v>
+        <v>71</v>
       </c>
       <c r="R19" t="n">
+        <v>74</v>
+      </c>
+      <c r="S19" t="n">
         <v>32</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>37.6</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>32.2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>51.6</v>
       </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.028546466482447</v>
-      </c>
-      <c r="X19" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.124321232800446</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1995,30 +2054,33 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>94.2192</v>
+        <v>76</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.1</v>
+        <v>71</v>
       </c>
       <c r="R20" t="n">
+        <v>74</v>
+      </c>
+      <c r="S20" t="n">
         <v>32.4</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>37.8</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>32.4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>52</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.057804966627766</v>
-      </c>
-      <c r="X20" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.110010122065204</v>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2073,30 +2135,33 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>93.0192</v>
+        <v>76</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.74</v>
+        <v>71</v>
       </c>
       <c r="R21" t="n">
+        <v>74</v>
+      </c>
+      <c r="S21" t="n">
         <v>32.8</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>38</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>31.8</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>51.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.013774292211443</v>
-      </c>
-      <c r="X21" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.012097807738467</v>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2151,30 +2216,33 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.74</v>
+        <v>71</v>
       </c>
       <c r="R22" t="n">
+        <v>74</v>
+      </c>
+      <c r="S22" t="n">
         <v>33.2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>38.6</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>31</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>50.6</v>
       </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
       <c r="W22" t="n">
-        <v>0.9916761238491784</v>
-      </c>
-      <c r="X22" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01099417044956</v>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2229,30 +2297,33 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>94.2</v>
+        <v>76</v>
       </c>
       <c r="Q23" t="n">
-        <v>19.1</v>
+        <v>71</v>
       </c>
       <c r="R23" t="n">
+        <v>74</v>
+      </c>
+      <c r="S23" t="n">
         <v>32.6</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>38.2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>30.6</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>50.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="W23" t="n">
-        <v>0.9872284490190244</v>
-      </c>
-      <c r="X23" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.011009148937534</v>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2307,30 +2378,33 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q24" t="n">
-        <v>19.5</v>
+        <v>71</v>
       </c>
       <c r="R24" t="n">
+        <v>74</v>
+      </c>
+      <c r="S24" t="n">
         <v>32.2</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>37.8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>31</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>51</v>
       </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="W24" t="n">
-        <v>0.9918317574383488</v>
-      </c>
-      <c r="X24" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9751700954027539</v>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2385,30 +2459,33 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q25" t="n">
-        <v>20.26</v>
+        <v>71</v>
       </c>
       <c r="R25" t="n">
+        <v>74</v>
+      </c>
+      <c r="S25" t="n">
         <v>32</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>37.6</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>31</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>51.4</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
       <c r="W25" t="n">
-        <v>0.9994066610954391</v>
-      </c>
-      <c r="X25" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9716984239732552</v>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2463,30 +2540,33 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>97.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.36</v>
+        <v>71</v>
       </c>
       <c r="R26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S26" t="n">
         <v>32.2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>37.2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>31</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>51.6</v>
       </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
       <c r="W26" t="n">
-        <v>0.9989070548648098</v>
-      </c>
-      <c r="X26" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9701222049890609</v>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2541,30 +2621,33 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.56</v>
+        <v>71</v>
       </c>
       <c r="R27" t="n">
+        <v>74</v>
+      </c>
+      <c r="S27" t="n">
         <v>32.4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>37.2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>31.4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>51.8</v>
       </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
-        <v>0.9902572379560487</v>
-      </c>
-      <c r="X27" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.9837755046057014</v>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2619,30 +2702,33 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.2</v>
+        <v>71</v>
       </c>
       <c r="R28" t="n">
+        <v>74</v>
+      </c>
+      <c r="S28" t="n">
         <v>33.2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>38.2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>31.2</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>51.4</v>
       </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
-        <v>0.9722076444681458</v>
-      </c>
-      <c r="X28" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.9847289520607756</v>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2697,30 +2783,33 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>98.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.6</v>
+        <v>71</v>
       </c>
       <c r="R29" t="n">
+        <v>74</v>
+      </c>
+      <c r="S29" t="n">
         <v>33.6</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>38.8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>30.4</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>50.8</v>
       </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.031114994038154</v>
-      </c>
-      <c r="X29" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.011897910587817</v>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2775,30 +2864,33 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q30" t="n">
-        <v>19.46</v>
+        <v>71</v>
       </c>
       <c r="R30" t="n">
+        <v>74</v>
+      </c>
+      <c r="S30" t="n">
         <v>33.8</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>39.2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>30</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>50.4</v>
       </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.052515368494723</v>
-      </c>
-      <c r="X30" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.073668016095711</v>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2853,30 +2945,33 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="Q31" t="n">
-        <v>18.66</v>
+        <v>71</v>
       </c>
       <c r="R31" t="n">
+        <v>74</v>
+      </c>
+      <c r="S31" t="n">
         <v>33.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>39.4</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>29.8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>50.6</v>
       </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.024715809881892</v>
-      </c>
-      <c r="X31" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.086690539217047</v>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2931,30 +3026,33 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>101.8</v>
+        <v>76</v>
       </c>
       <c r="Q32" t="n">
-        <v>19.06</v>
+        <v>71</v>
       </c>
       <c r="R32" t="n">
+        <v>74</v>
+      </c>
+      <c r="S32" t="n">
         <v>33.4</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>39.2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>29.6</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>50.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.024480013969423</v>
-      </c>
-      <c r="X32" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.080521366127174</v>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3009,30 +3107,33 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>98.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q33" t="n">
-        <v>20.26</v>
+        <v>71</v>
       </c>
       <c r="R33" t="n">
+        <v>74</v>
+      </c>
+      <c r="S33" t="n">
         <v>32.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>37.6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>29.8</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>51.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.076301156628274</v>
-      </c>
-      <c r="X33" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.108477124478552</v>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3087,30 +3188,33 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q34" t="n">
-        <v>21.86</v>
+        <v>71</v>
       </c>
       <c r="R34" t="n">
+        <v>74</v>
+      </c>
+      <c r="S34" t="n">
         <v>32.6</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>37</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>30.2</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>52.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.009748195262052</v>
-      </c>
-      <c r="X34" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.265258441425686</v>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3165,32 +3269,35 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>92.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.32</v>
+        <v>71</v>
       </c>
       <c r="R35" t="n">
+        <v>74</v>
+      </c>
+      <c r="S35" t="n">
         <v>32.6</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>36.6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>30.6</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>53.2</v>
       </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
       <c r="W35" t="n">
-        <v>1.203976731906644</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.428279746887389</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3243,32 +3350,35 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>91</v>
+        <v>76.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.12</v>
+        <v>70.8</v>
       </c>
       <c r="R36" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S36" t="n">
         <v>32.6</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>36.6</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>30.4</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>53.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="W36" t="n">
-        <v>1.009610168762611</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.671646186391665</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3431,35 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>89.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.62</v>
+        <v>70.8</v>
       </c>
       <c r="R37" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S37" t="n">
         <v>32.6</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>36.8</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>30.4</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>52.8</v>
       </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="W37" t="n">
-        <v>1.009970781685876</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.672535585686214</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -3399,32 +3512,35 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>91.2</v>
+        <v>76.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>19.62</v>
+        <v>70.8</v>
       </c>
       <c r="R38" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S38" t="n">
         <v>32.8</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>37.2</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>30.2</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>51.8</v>
       </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
       <c r="W38" t="n">
-        <v>1.009532214306178</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.589588400237924</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3593,35 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>92.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>17.88</v>
+        <v>70.8</v>
       </c>
       <c r="R39" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S39" t="n">
         <v>32.2</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>36.4</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>30.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>51.6</v>
       </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
       <c r="W39" t="n">
-        <v>0.9863850985841058</v>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.538024294751703</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3555,30 +3674,33 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.3</v>
+        <v>70.8</v>
       </c>
       <c r="R40" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S40" t="n">
         <v>31.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>36.2</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>30.4</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>52</v>
       </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
       <c r="W40" t="n">
-        <v>0.990651119592213</v>
-      </c>
-      <c r="X40" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.262085260674866</v>
+      </c>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3633,30 +3755,33 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q41" t="n">
-        <v>19.88</v>
+        <v>71</v>
       </c>
       <c r="R41" t="n">
+        <v>74</v>
+      </c>
+      <c r="S41" t="n">
         <v>30.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>36</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>31</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>52.4</v>
       </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
       <c r="W41" t="n">
-        <v>1.003600086132721</v>
-      </c>
-      <c r="X41" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.063533455486001</v>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3711,30 +3836,33 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>91.2</v>
+        <v>76</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.38</v>
+        <v>71</v>
       </c>
       <c r="R42" t="n">
+        <v>74</v>
+      </c>
+      <c r="S42" t="n">
         <v>29.2</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>35.6</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>31.4</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>53.2</v>
       </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
       <c r="W42" t="n">
-        <v>1.069262862643484</v>
-      </c>
-      <c r="X42" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.142385017023178</v>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3789,30 +3917,33 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q43" t="n">
-        <v>22.5</v>
+        <v>71</v>
       </c>
       <c r="R43" t="n">
+        <v>74</v>
+      </c>
+      <c r="S43" t="n">
         <v>29.2</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>37</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>31.6</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>54</v>
       </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
       <c r="W43" t="n">
-        <v>1.04774860029322</v>
-      </c>
-      <c r="X43" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.201648838735862</v>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3867,32 +3998,35 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>90.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q44" t="n">
-        <v>22.98</v>
+        <v>71</v>
       </c>
       <c r="R44" t="n">
+        <v>74</v>
+      </c>
+      <c r="S44" t="n">
         <v>30</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>38.6</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>31.6</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>53.4</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
       <c r="W44" t="n">
-        <v>1.027664366623089</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.501246798628404</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3945,32 +4079,35 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>89.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q45" t="n">
-        <v>21.78</v>
+        <v>71</v>
       </c>
       <c r="R45" t="n">
+        <v>74</v>
+      </c>
+      <c r="S45" t="n">
         <v>31</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>39.4</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>31.4</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>52.8</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
       <c r="W45" t="n">
-        <v>1.027353297238565</v>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.372679551310955</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -4023,30 +4160,33 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>88.2</v>
+        <v>76</v>
       </c>
       <c r="Q46" t="n">
-        <v>19.5</v>
+        <v>71</v>
       </c>
       <c r="R46" t="n">
+        <v>74</v>
+      </c>
+      <c r="S46" t="n">
         <v>31.2</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>38.4</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>30.8</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>52.2</v>
       </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
       <c r="W46" t="n">
-        <v>1.193768200649983</v>
-      </c>
-      <c r="X46" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.995374537264636</v>
+      </c>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4101,30 +4241,33 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>90.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q47" t="n">
-        <v>18.1</v>
+        <v>71</v>
       </c>
       <c r="R47" t="n">
+        <v>74</v>
+      </c>
+      <c r="S47" t="n">
         <v>31.6</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>37.6</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>31</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>52</v>
       </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
       <c r="W47" t="n">
-        <v>1.010222681633885</v>
-      </c>
-      <c r="X47" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.9829324892539223</v>
+      </c>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4179,30 +4322,33 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q48" t="n">
-        <v>18.5</v>
+        <v>71</v>
       </c>
       <c r="R48" t="n">
+        <v>74</v>
+      </c>
+      <c r="S48" t="n">
         <v>31</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>36</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>31.4</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>51.8</v>
       </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
       <c r="W48" t="n">
-        <v>0.982998732188024</v>
-      </c>
-      <c r="X48" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.15262301022536</v>
+      </c>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4257,30 +4403,33 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.16</v>
+        <v>71</v>
       </c>
       <c r="R49" t="n">
+        <v>74</v>
+      </c>
+      <c r="S49" t="n">
         <v>30.4</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>35.2</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>31.8</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>52.2</v>
       </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
       <c r="W49" t="n">
-        <v>1.039092260715537</v>
-      </c>
-      <c r="X49" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.210697898709775</v>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4335,30 +4484,33 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.76</v>
+        <v>71</v>
       </c>
       <c r="R50" t="n">
+        <v>74</v>
+      </c>
+      <c r="S50" t="n">
         <v>30.2</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>34.4</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>32</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>52.6</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
       <c r="W50" t="n">
-        <v>1.303298623743227</v>
-      </c>
-      <c r="X50" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.367051813337393</v>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -4413,30 +4565,33 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q51" t="n">
-        <v>22.98</v>
+        <v>71</v>
       </c>
       <c r="R51" t="n">
+        <v>74</v>
+      </c>
+      <c r="S51" t="n">
         <v>30.8</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>35.8</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>32.2</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>52.8</v>
       </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
       <c r="W51" t="n">
-        <v>1.093511018308645</v>
-      </c>
-      <c r="X51" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.190136361585474</v>
+      </c>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4491,30 +4646,33 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.46</v>
+        <v>71</v>
       </c>
       <c r="R52" t="n">
+        <v>74</v>
+      </c>
+      <c r="S52" t="n">
         <v>31.2</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>37</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>31.6</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>52.6</v>
       </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
       <c r="W52" t="n">
-        <v>1.071584286088626</v>
-      </c>
-      <c r="X52" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.023670776645364</v>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4569,30 +4727,33 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q53" t="n">
-        <v>22.34</v>
+        <v>71</v>
       </c>
       <c r="R53" t="n">
+        <v>74</v>
+      </c>
+      <c r="S53" t="n">
         <v>31.6</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>38.2</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>31</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>52.4</v>
       </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
       <c r="W53" t="n">
-        <v>1.00846361094</v>
-      </c>
-      <c r="X53" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.9817943339921289</v>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4647,30 +4808,33 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.2</v>
+        <v>71</v>
       </c>
       <c r="R54" t="n">
+        <v>74</v>
+      </c>
+      <c r="S54" t="n">
         <v>32</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>38.6</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>30.4</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>51.6</v>
       </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
       <c r="W54" t="n">
-        <v>0.9897110939096889</v>
-      </c>
-      <c r="X54" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.9945708479442427</v>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4725,30 +4889,33 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q55" t="n">
-        <v>18.68</v>
+        <v>71</v>
       </c>
       <c r="R55" t="n">
+        <v>74</v>
+      </c>
+      <c r="S55" t="n">
         <v>32</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>38.8</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>30.2</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>51.4</v>
       </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
       <c r="W55" t="n">
-        <v>1.014489592182561</v>
-      </c>
-      <c r="X55" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.002011327063128</v>
+      </c>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4803,30 +4970,33 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.64</v>
+        <v>71</v>
       </c>
       <c r="R56" t="n">
+        <v>74</v>
+      </c>
+      <c r="S56" t="n">
         <v>31.8</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>38</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>30.6</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>51.6</v>
       </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
       <c r="W56" t="n">
-        <v>0.9816958731022458</v>
-      </c>
-      <c r="X56" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.9682786168517861</v>
+      </c>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4881,30 +5051,33 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q57" t="n">
-        <v>21.56</v>
+        <v>71</v>
       </c>
       <c r="R57" t="n">
+        <v>74</v>
+      </c>
+      <c r="S57" t="n">
         <v>31.8</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>37.6</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>31</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>51.8</v>
       </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
       <c r="W57" t="n">
-        <v>0.9806097659934953</v>
-      </c>
-      <c r="X57" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.9786427821755177</v>
+      </c>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4959,30 +5132,33 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.16</v>
+        <v>71</v>
       </c>
       <c r="R58" t="n">
+        <v>74</v>
+      </c>
+      <c r="S58" t="n">
         <v>31.8</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>37.2</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>31.4</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>52</v>
       </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
       <c r="W58" t="n">
-        <v>1.024965902338576</v>
-      </c>
-      <c r="X58" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.9707591696971711</v>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5037,30 +5213,33 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q59" t="n">
-        <v>24.7</v>
+        <v>71</v>
       </c>
       <c r="R59" t="n">
+        <v>74</v>
+      </c>
+      <c r="S59" t="n">
         <v>31.8</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>37.2</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>31.4</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>52.8</v>
       </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
       <c r="W59" t="n">
-        <v>0.9899327643731493</v>
-      </c>
-      <c r="X59" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.9787014758708423</v>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5115,30 +5294,33 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>95.8</v>
+        <v>76</v>
       </c>
       <c r="Q60" t="n">
-        <v>25.22</v>
+        <v>71</v>
       </c>
       <c r="R60" t="n">
+        <v>74</v>
+      </c>
+      <c r="S60" t="n">
         <v>32.2</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>37.8</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>31.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>52.8</v>
       </c>
-      <c r="V60" t="n">
-        <v>1</v>
-      </c>
       <c r="W60" t="n">
-        <v>0.9935318264133253</v>
-      </c>
-      <c r="X60" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.9562370147841838</v>
+      </c>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5193,30 +5375,33 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q61" t="n">
-        <v>23.8</v>
+        <v>71</v>
       </c>
       <c r="R61" t="n">
+        <v>74</v>
+      </c>
+      <c r="S61" t="n">
         <v>32.6</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>38.6</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>30.8</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>52.4</v>
       </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
       <c r="W61" t="n">
-        <v>0.9916577626390517</v>
-      </c>
-      <c r="X61" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.001728565131534</v>
+      </c>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5271,30 +5456,33 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q62" t="n">
-        <v>21.4</v>
+        <v>71</v>
       </c>
       <c r="R62" t="n">
+        <v>74</v>
+      </c>
+      <c r="S62" t="n">
         <v>32.8</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>39</v>
       </c>
-      <c r="T62" t="n">
+      <c r="U62" t="n">
         <v>30.4</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>52</v>
       </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
       <c r="W62" t="n">
-        <v>0.9897615217310849</v>
-      </c>
-      <c r="X62" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.000847267482377</v>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5349,30 +5537,33 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q63" t="n">
-        <v>21.4</v>
+        <v>71</v>
       </c>
       <c r="R63" t="n">
+        <v>74</v>
+      </c>
+      <c r="S63" t="n">
         <v>32.2</v>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="n">
         <v>38.6</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>29.8</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>51.6</v>
       </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
       <c r="W63" t="n">
-        <v>0.9968072245606872</v>
-      </c>
-      <c r="X63" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.066734284149733</v>
+      </c>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5427,30 +5618,33 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q64" t="n">
-        <v>22.28</v>
+        <v>71</v>
       </c>
       <c r="R64" t="n">
+        <v>74</v>
+      </c>
+      <c r="S64" t="n">
         <v>32</v>
       </c>
-      <c r="S64" t="n">
+      <c r="T64" t="n">
         <v>38.2</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>30.2</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>51.8</v>
       </c>
-      <c r="V64" t="n">
-        <v>1</v>
-      </c>
       <c r="W64" t="n">
-        <v>0.9784551634861742</v>
-      </c>
-      <c r="X64" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.000331444306329</v>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5505,30 +5699,33 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q65" t="n">
-        <v>23.44</v>
+        <v>71</v>
       </c>
       <c r="R65" t="n">
+        <v>74</v>
+      </c>
+      <c r="S65" t="n">
         <v>31.4</v>
       </c>
-      <c r="S65" t="n">
+      <c r="T65" t="n">
         <v>37.4</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>30.6</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>52.2</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
       <c r="W65" t="n">
-        <v>1.00113656465327</v>
-      </c>
-      <c r="X65" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.9686694098449447</v>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5583,30 +5780,33 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q66" t="n">
-        <v>24.44</v>
+        <v>71</v>
       </c>
       <c r="R66" t="n">
+        <v>74</v>
+      </c>
+      <c r="S66" t="n">
         <v>31.4</v>
       </c>
-      <c r="S66" t="n">
+      <c r="T66" t="n">
         <v>37.4</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>30.8</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>52.4</v>
       </c>
-      <c r="V66" t="n">
-        <v>1</v>
-      </c>
       <c r="W66" t="n">
-        <v>1.023863813693654</v>
-      </c>
-      <c r="X66" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.9726345910837884</v>
+      </c>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5661,30 +5861,33 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q67" t="n">
-        <v>25.34</v>
+        <v>71</v>
       </c>
       <c r="R67" t="n">
+        <v>74</v>
+      </c>
+      <c r="S67" t="n">
         <v>31.4</v>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="n">
         <v>37.4</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>31</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>52.6</v>
       </c>
-      <c r="V67" t="n">
-        <v>1</v>
-      </c>
       <c r="W67" t="n">
-        <v>0.995215482629859</v>
-      </c>
-      <c r="X67" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.9708033665566204</v>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5739,30 +5942,33 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q68" t="n">
-        <v>23.72</v>
+        <v>71</v>
       </c>
       <c r="R68" t="n">
+        <v>74</v>
+      </c>
+      <c r="S68" t="n">
         <v>32.2</v>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="n">
         <v>38.6</v>
       </c>
-      <c r="T68" t="n">
+      <c r="U68" t="n">
         <v>31.4</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>52.6</v>
       </c>
-      <c r="V68" t="n">
-        <v>1</v>
-      </c>
       <c r="W68" t="n">
-        <v>0.9999781727672665</v>
-      </c>
-      <c r="X68" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1.028750708547116</v>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5817,30 +6023,33 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q69" t="n">
-        <v>21.36</v>
+        <v>71</v>
       </c>
       <c r="R69" t="n">
+        <v>74</v>
+      </c>
+      <c r="S69" t="n">
         <v>32.6</v>
       </c>
-      <c r="S69" t="n">
+      <c r="T69" t="n">
         <v>39</v>
       </c>
-      <c r="T69" t="n">
+      <c r="U69" t="n">
         <v>30.8</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>51.8</v>
       </c>
-      <c r="V69" t="n">
-        <v>1</v>
-      </c>
       <c r="W69" t="n">
-        <v>0.9917020178388982</v>
-      </c>
-      <c r="X69" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.007646204635518</v>
+      </c>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5895,30 +6104,33 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q70" t="n">
-        <v>19.2</v>
+        <v>71</v>
       </c>
       <c r="R70" t="n">
+        <v>74</v>
+      </c>
+      <c r="S70" t="n">
         <v>33</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>39.4</v>
       </c>
-      <c r="T70" t="n">
+      <c r="U70" t="n">
         <v>30.4</v>
       </c>
-      <c r="U70" t="n">
+      <c r="V70" t="n">
         <v>51</v>
       </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
       <c r="W70" t="n">
-        <v>0.9906218833117968</v>
-      </c>
-      <c r="X70" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.019677769005965</v>
+      </c>
+      <c r="Y70" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5973,30 +6185,33 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q71" t="n">
-        <v>19.4</v>
+        <v>71</v>
       </c>
       <c r="R71" t="n">
+        <v>74</v>
+      </c>
+      <c r="S71" t="n">
         <v>33</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>39.4</v>
       </c>
-      <c r="T71" t="n">
+      <c r="U71" t="n">
         <v>30.2</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>50.6</v>
       </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
       <c r="W71" t="n">
-        <v>0.998189998939127</v>
-      </c>
-      <c r="X71" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.045328834461783</v>
+      </c>
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6051,30 +6266,33 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>96.2</v>
+        <v>76</v>
       </c>
       <c r="Q72" t="n">
-        <v>20.7</v>
+        <v>71</v>
       </c>
       <c r="R72" t="n">
+        <v>74</v>
+      </c>
+      <c r="S72" t="n">
         <v>33</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>38.8</v>
       </c>
-      <c r="T72" t="n">
+      <c r="U72" t="n">
         <v>30.6</v>
       </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
         <v>50.8</v>
       </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
       <c r="W72" t="n">
-        <v>0.9949153790730378</v>
-      </c>
-      <c r="X72" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.9888886997937287</v>
+      </c>
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6129,30 +6347,33 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q73" t="n">
-        <v>22.32</v>
+        <v>71</v>
       </c>
       <c r="R73" t="n">
+        <v>74</v>
+      </c>
+      <c r="S73" t="n">
         <v>33</v>
       </c>
-      <c r="S73" t="n">
+      <c r="T73" t="n">
         <v>38.2</v>
       </c>
-      <c r="T73" t="n">
+      <c r="U73" t="n">
         <v>30.6</v>
       </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
         <v>51.2</v>
       </c>
-      <c r="V73" t="n">
-        <v>1</v>
-      </c>
       <c r="W73" t="n">
-        <v>0.991098742962758</v>
-      </c>
-      <c r="X73" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.9598271895076804</v>
+      </c>
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6207,30 +6428,33 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q74" t="n">
-        <v>23.64</v>
+        <v>71</v>
       </c>
       <c r="R74" t="n">
+        <v>74</v>
+      </c>
+      <c r="S74" t="n">
         <v>33.6</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>38.2</v>
       </c>
-      <c r="T74" t="n">
+      <c r="U74" t="n">
         <v>31.2</v>
       </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
         <v>52</v>
       </c>
-      <c r="V74" t="n">
-        <v>1</v>
-      </c>
       <c r="W74" t="n">
-        <v>0.9903323949387837</v>
-      </c>
-      <c r="X74" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.9889045681184309</v>
+      </c>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6285,30 +6509,33 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>97.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q75" t="n">
-        <v>24.54</v>
+        <v>71</v>
       </c>
       <c r="R75" t="n">
+        <v>74</v>
+      </c>
+      <c r="S75" t="n">
         <v>33.8</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>38.6</v>
       </c>
-      <c r="T75" t="n">
+      <c r="U75" t="n">
         <v>31.4</v>
       </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
         <v>52.4</v>
       </c>
-      <c r="V75" t="n">
-        <v>1</v>
-      </c>
       <c r="W75" t="n">
-        <v>0.9997029610138505</v>
-      </c>
-      <c r="X75" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.037584498613392</v>
+      </c>
+      <c r="Y75" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6363,30 +6590,33 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q76" t="n">
-        <v>23.14</v>
+        <v>71</v>
       </c>
       <c r="R76" t="n">
+        <v>74</v>
+      </c>
+      <c r="S76" t="n">
         <v>34</v>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>39</v>
       </c>
-      <c r="T76" t="n">
+      <c r="U76" t="n">
         <v>31.6</v>
       </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
         <v>52.8</v>
       </c>
-      <c r="V76" t="n">
-        <v>1</v>
-      </c>
       <c r="W76" t="n">
-        <v>1.046711438961913</v>
-      </c>
-      <c r="X76" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.285167460752966</v>
+      </c>
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6441,30 +6671,33 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q77" t="n">
-        <v>20.86</v>
+        <v>71</v>
       </c>
       <c r="R77" t="n">
+        <v>74</v>
+      </c>
+      <c r="S77" t="n">
         <v>32.6</v>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="n">
         <v>38.4</v>
       </c>
-      <c r="T77" t="n">
+      <c r="U77" t="n">
         <v>31</v>
       </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
         <v>52.4</v>
       </c>
-      <c r="V77" t="n">
-        <v>1</v>
-      </c>
       <c r="W77" t="n">
-        <v>0.9917018683382091</v>
-      </c>
-      <c r="X77" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0.9821339471250781</v>
+      </c>
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6519,30 +6752,33 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q78" t="n">
-        <v>20.66</v>
+        <v>71</v>
       </c>
       <c r="R78" t="n">
+        <v>74</v>
+      </c>
+      <c r="S78" t="n">
         <v>31.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>37.4</v>
       </c>
-      <c r="T78" t="n">
+      <c r="U78" t="n">
         <v>30.8</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
         <v>52.2</v>
       </c>
-      <c r="V78" t="n">
-        <v>1</v>
-      </c>
       <c r="W78" t="n">
-        <v>1.004865838804076</v>
-      </c>
-      <c r="X78" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.9717535682807956</v>
+      </c>
+      <c r="Y78" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6597,30 +6833,33 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="Q79" t="n">
-        <v>21.7</v>
+        <v>71</v>
       </c>
       <c r="R79" t="n">
+        <v>74</v>
+      </c>
+      <c r="S79" t="n">
         <v>29.6</v>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>36.2</v>
       </c>
-      <c r="T79" t="n">
+      <c r="U79" t="n">
         <v>30.4</v>
       </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
         <v>51.8</v>
       </c>
-      <c r="V79" t="n">
-        <v>1</v>
-      </c>
       <c r="W79" t="n">
-        <v>1.037273396914064</v>
-      </c>
-      <c r="X79" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.122554801200156</v>
+      </c>
+      <c r="Y79" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6675,30 +6914,33 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="Q80" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="R80" t="n">
+        <v>74</v>
+      </c>
+      <c r="S80" t="n">
         <v>28.2</v>
       </c>
-      <c r="S80" t="n">
+      <c r="T80" t="n">
         <v>34.6</v>
       </c>
-      <c r="T80" t="n">
+      <c r="U80" t="n">
         <v>30.2</v>
       </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
         <v>51.8</v>
       </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
       <c r="W80" t="n">
-        <v>1.129500705806051</v>
-      </c>
-      <c r="X80" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1.233489483138686</v>
+      </c>
+      <c r="Y80" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6753,30 +6995,33 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>89.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q81" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="R81" t="n">
+        <v>74</v>
+      </c>
+      <c r="S81" t="n">
         <v>28</v>
       </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
         <v>34.2</v>
       </c>
-      <c r="T81" t="n">
+      <c r="U81" t="n">
         <v>30.2</v>
       </c>
-      <c r="U81" t="n">
+      <c r="V81" t="n">
         <v>51.8</v>
       </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
       <c r="W81" t="n">
-        <v>1.213891474617561</v>
-      </c>
-      <c r="X81" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1.259255425259055</v>
+      </c>
+      <c r="Y81" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6831,30 +7076,33 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>90.2</v>
+        <v>76</v>
       </c>
       <c r="Q82" t="n">
-        <v>25.02</v>
+        <v>71</v>
       </c>
       <c r="R82" t="n">
+        <v>74</v>
+      </c>
+      <c r="S82" t="n">
         <v>29.4</v>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
         <v>35.4</v>
       </c>
-      <c r="T82" t="n">
+      <c r="U82" t="n">
         <v>30.4</v>
       </c>
-      <c r="U82" t="n">
+      <c r="V82" t="n">
         <v>52</v>
       </c>
-      <c r="V82" t="n">
-        <v>1</v>
-      </c>
       <c r="W82" t="n">
-        <v>1.213263103125219</v>
-      </c>
-      <c r="X82" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1.123872918423256</v>
+      </c>
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6909,30 +7157,33 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q83" t="n">
-        <v>23.74</v>
+        <v>71</v>
       </c>
       <c r="R83" t="n">
+        <v>74</v>
+      </c>
+      <c r="S83" t="n">
         <v>30.6</v>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="n">
         <v>36.6</v>
       </c>
-      <c r="T83" t="n">
+      <c r="U83" t="n">
         <v>30.6</v>
       </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
         <v>52</v>
       </c>
-      <c r="V83" t="n">
-        <v>1</v>
-      </c>
       <c r="W83" t="n">
-        <v>1.113648929594026</v>
-      </c>
-      <c r="X83" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X83" t="n">
+        <v>1.061849359147477</v>
+      </c>
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6987,30 +7238,33 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="Q84" t="n">
-        <v>21.26</v>
+        <v>71</v>
       </c>
       <c r="R84" t="n">
+        <v>74</v>
+      </c>
+      <c r="S84" t="n">
         <v>31.8</v>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="n">
         <v>37.8</v>
       </c>
-      <c r="T84" t="n">
+      <c r="U84" t="n">
         <v>30.8</v>
       </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
         <v>52</v>
       </c>
-      <c r="V84" t="n">
-        <v>1</v>
-      </c>
       <c r="W84" t="n">
-        <v>0.9842469360900049</v>
-      </c>
-      <c r="X84" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0.9846339428664861</v>
+      </c>
+      <c r="Y84" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7065,30 +7319,33 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q85" t="n">
-        <v>20.64</v>
+        <v>71</v>
       </c>
       <c r="R85" t="n">
+        <v>74</v>
+      </c>
+      <c r="S85" t="n">
         <v>32.6</v>
       </c>
-      <c r="S85" t="n">
+      <c r="T85" t="n">
         <v>38.6</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>31.2</v>
       </c>
-      <c r="U85" t="n">
+      <c r="V85" t="n">
         <v>52.2</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
       <c r="W85" t="n">
-        <v>0.9937303933799411</v>
-      </c>
-      <c r="X85" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.9860537100922331</v>
+      </c>
+      <c r="Y85" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7143,30 +7400,33 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q86" t="n">
-        <v>21.68</v>
+        <v>71</v>
       </c>
       <c r="R86" t="n">
+        <v>74</v>
+      </c>
+      <c r="S86" t="n">
         <v>32.2</v>
       </c>
-      <c r="S86" t="n">
+      <c r="T86" t="n">
         <v>38.2</v>
       </c>
-      <c r="T86" t="n">
+      <c r="U86" t="n">
         <v>31.4</v>
       </c>
-      <c r="U86" t="n">
+      <c r="V86" t="n">
         <v>52.4</v>
       </c>
-      <c r="V86" t="n">
-        <v>1</v>
-      </c>
       <c r="W86" t="n">
-        <v>0.9924480536558841</v>
-      </c>
-      <c r="X86" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.9715875830471319</v>
+      </c>
+      <c r="Y86" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7221,30 +7481,33 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q87" t="n">
-        <v>22.54</v>
+        <v>71</v>
       </c>
       <c r="R87" t="n">
+        <v>74</v>
+      </c>
+      <c r="S87" t="n">
         <v>32.4</v>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="n">
         <v>37.6</v>
       </c>
-      <c r="T87" t="n">
+      <c r="U87" t="n">
         <v>31.8</v>
       </c>
-      <c r="U87" t="n">
+      <c r="V87" t="n">
         <v>53</v>
       </c>
-      <c r="V87" t="n">
-        <v>1</v>
-      </c>
       <c r="W87" t="n">
-        <v>1.017136061666243</v>
-      </c>
-      <c r="X87" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.9972246176334671</v>
+      </c>
+      <c r="Y87" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7299,30 +7562,33 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q88" t="n">
-        <v>23.68</v>
+        <v>71</v>
       </c>
       <c r="R88" t="n">
+        <v>74</v>
+      </c>
+      <c r="S88" t="n">
         <v>32.6</v>
       </c>
-      <c r="S88" t="n">
+      <c r="T88" t="n">
         <v>37.4</v>
       </c>
-      <c r="T88" t="n">
+      <c r="U88" t="n">
         <v>32</v>
       </c>
-      <c r="U88" t="n">
+      <c r="V88" t="n">
         <v>53</v>
       </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
       <c r="W88" t="n">
-        <v>1.013694680208678</v>
-      </c>
-      <c r="X88" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1.032524192207244</v>
+      </c>
+      <c r="Y88" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7377,30 +7643,33 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q89" t="n">
-        <v>24.68</v>
+        <v>71</v>
       </c>
       <c r="R89" t="n">
+        <v>74</v>
+      </c>
+      <c r="S89" t="n">
         <v>32.6</v>
       </c>
-      <c r="S89" t="n">
+      <c r="T89" t="n">
         <v>37.2</v>
       </c>
-      <c r="T89" t="n">
+      <c r="U89" t="n">
         <v>32</v>
       </c>
-      <c r="U89" t="n">
+      <c r="V89" t="n">
         <v>53</v>
       </c>
-      <c r="V89" t="n">
-        <v>1</v>
-      </c>
       <c r="W89" t="n">
-        <v>1.004166438298243</v>
-      </c>
-      <c r="X89" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1.04462863655203</v>
+      </c>
+      <c r="Y89" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7455,30 +7724,33 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q90" t="n">
-        <v>23.36</v>
+        <v>71</v>
       </c>
       <c r="R90" t="n">
+        <v>74</v>
+      </c>
+      <c r="S90" t="n">
         <v>33</v>
       </c>
-      <c r="S90" t="n">
+      <c r="T90" t="n">
         <v>37.4</v>
       </c>
-      <c r="T90" t="n">
+      <c r="U90" t="n">
         <v>31.8</v>
       </c>
-      <c r="U90" t="n">
+      <c r="V90" t="n">
         <v>52.8</v>
       </c>
-      <c r="V90" t="n">
-        <v>1</v>
-      </c>
       <c r="W90" t="n">
-        <v>0.9938932718787722</v>
-      </c>
-      <c r="X90" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1.012546182640755</v>
+      </c>
+      <c r="Y90" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7533,30 +7805,33 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q91" t="n">
-        <v>21.32</v>
+        <v>71</v>
       </c>
       <c r="R91" t="n">
+        <v>74</v>
+      </c>
+      <c r="S91" t="n">
         <v>33.4</v>
       </c>
-      <c r="S91" t="n">
+      <c r="T91" t="n">
         <v>37.4</v>
       </c>
-      <c r="T91" t="n">
+      <c r="U91" t="n">
         <v>32</v>
       </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
         <v>53</v>
       </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
       <c r="W91" t="n">
-        <v>1.079423358749453</v>
-      </c>
-      <c r="X91" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1.094303016124388</v>
+      </c>
+      <c r="Y91" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7611,30 +7886,33 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>99.8</v>
+        <v>76</v>
       </c>
       <c r="Q92" t="n">
-        <v>21.56</v>
+        <v>71</v>
       </c>
       <c r="R92" t="n">
+        <v>74</v>
+      </c>
+      <c r="S92" t="n">
         <v>33</v>
       </c>
-      <c r="S92" t="n">
+      <c r="T92" t="n">
         <v>37.6</v>
       </c>
-      <c r="T92" t="n">
+      <c r="U92" t="n">
         <v>31.8</v>
       </c>
-      <c r="U92" t="n">
+      <c r="V92" t="n">
         <v>52.8</v>
       </c>
-      <c r="V92" t="n">
-        <v>1</v>
-      </c>
       <c r="W92" t="n">
-        <v>1.086623460233822</v>
-      </c>
-      <c r="X92" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1.001650496988765</v>
+      </c>
+      <c r="Y92" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7689,30 +7967,33 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="Q93" t="n">
-        <v>22.14</v>
+        <v>71</v>
       </c>
       <c r="R93" t="n">
+        <v>74</v>
+      </c>
+      <c r="S93" t="n">
         <v>32.6</v>
       </c>
-      <c r="S93" t="n">
+      <c r="T93" t="n">
         <v>37.4</v>
       </c>
-      <c r="T93" t="n">
+      <c r="U93" t="n">
         <v>31.8</v>
       </c>
-      <c r="U93" t="n">
+      <c r="V93" t="n">
         <v>53.2</v>
       </c>
-      <c r="V93" t="n">
-        <v>1</v>
-      </c>
       <c r="W93" t="n">
-        <v>1.127745229221297</v>
-      </c>
-      <c r="X93" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1.009759397701603</v>
+      </c>
+      <c r="Y93" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7767,30 +8048,33 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q94" t="n">
-        <v>22.34</v>
+        <v>71</v>
       </c>
       <c r="R94" t="n">
+        <v>74</v>
+      </c>
+      <c r="S94" t="n">
         <v>32.8</v>
       </c>
-      <c r="S94" t="n">
+      <c r="T94" t="n">
         <v>37.8</v>
       </c>
-      <c r="T94" t="n">
+      <c r="U94" t="n">
         <v>31.8</v>
       </c>
-      <c r="U94" t="n">
+      <c r="V94" t="n">
         <v>53</v>
       </c>
-      <c r="V94" t="n">
-        <v>1</v>
-      </c>
       <c r="W94" t="n">
-        <v>1.100901211597081</v>
-      </c>
-      <c r="X94" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X94" t="n">
+        <v>1.008457685141113</v>
+      </c>
+      <c r="Y94" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7845,30 +8129,33 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q95" t="n">
-        <v>22.7</v>
+        <v>71</v>
       </c>
       <c r="R95" t="n">
+        <v>74</v>
+      </c>
+      <c r="S95" t="n">
         <v>33</v>
       </c>
-      <c r="S95" t="n">
+      <c r="T95" t="n">
         <v>37.8</v>
       </c>
-      <c r="T95" t="n">
+      <c r="U95" t="n">
         <v>31.8</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>52.8</v>
       </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
       <c r="W95" t="n">
-        <v>1.118908607468491</v>
-      </c>
-      <c r="X95" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1.00764791040326</v>
+      </c>
+      <c r="Y95" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7923,30 +8210,33 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>98.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q96" t="n">
-        <v>22.1</v>
+        <v>71</v>
       </c>
       <c r="R96" t="n">
+        <v>74</v>
+      </c>
+      <c r="S96" t="n">
         <v>33.2</v>
       </c>
-      <c r="S96" t="n">
+      <c r="T96" t="n">
         <v>38</v>
       </c>
-      <c r="T96" t="n">
+      <c r="U96" t="n">
         <v>31.4</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>52.2</v>
       </c>
-      <c r="V96" t="n">
-        <v>1</v>
-      </c>
       <c r="W96" t="n">
-        <v>1.024418609902379</v>
-      </c>
-      <c r="X96" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0.9776025482453449</v>
+      </c>
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8001,30 +8291,33 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="Q97" t="n">
-        <v>19.94</v>
+        <v>71</v>
       </c>
       <c r="R97" t="n">
+        <v>74</v>
+      </c>
+      <c r="S97" t="n">
         <v>33.4</v>
       </c>
-      <c r="S97" t="n">
+      <c r="T97" t="n">
         <v>37.6</v>
       </c>
-      <c r="T97" t="n">
+      <c r="U97" t="n">
         <v>31</v>
       </c>
-      <c r="U97" t="n">
+      <c r="V97" t="n">
         <v>51.4</v>
       </c>
-      <c r="V97" t="n">
-        <v>1</v>
-      </c>
       <c r="W97" t="n">
-        <v>1.062063246769027</v>
-      </c>
-      <c r="X97" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1.004963188991562</v>
+      </c>
+      <c r="Y97" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8079,30 +8372,33 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>97.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q98" t="n">
-        <v>19.72</v>
+        <v>71</v>
       </c>
       <c r="R98" t="n">
+        <v>74</v>
+      </c>
+      <c r="S98" t="n">
         <v>33.2</v>
       </c>
-      <c r="S98" t="n">
+      <c r="T98" t="n">
         <v>37.8</v>
       </c>
-      <c r="T98" t="n">
+      <c r="U98" t="n">
         <v>31</v>
       </c>
-      <c r="U98" t="n">
+      <c r="V98" t="n">
         <v>51.2</v>
       </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
       <c r="W98" t="n">
-        <v>1.006290758051299</v>
-      </c>
-      <c r="X98" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0.9883031390472278</v>
+      </c>
+      <c r="Y98" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8157,30 +8453,33 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q99" t="n">
-        <v>20.12</v>
+        <v>71</v>
       </c>
       <c r="R99" t="n">
+        <v>74</v>
+      </c>
+      <c r="S99" t="n">
         <v>32.6</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
         <v>37.4</v>
       </c>
-      <c r="T99" t="n">
+      <c r="U99" t="n">
         <v>31.2</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>51.6</v>
       </c>
-      <c r="V99" t="n">
-        <v>1</v>
-      </c>
       <c r="W99" t="n">
-        <v>0.9891826504592819</v>
-      </c>
-      <c r="X99" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0.9622535190562276</v>
+      </c>
+      <c r="Y99" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8235,30 +8534,33 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="Q100" t="n">
-        <v>20.3</v>
+        <v>71</v>
       </c>
       <c r="R100" t="n">
+        <v>74</v>
+      </c>
+      <c r="S100" t="n">
         <v>32.4</v>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
         <v>37.8</v>
       </c>
-      <c r="T100" t="n">
+      <c r="U100" t="n">
         <v>31.6</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>52</v>
       </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
       <c r="W100" t="n">
-        <v>0.984565266718454</v>
-      </c>
-      <c r="X100" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0.9857346420139349</v>
+      </c>
+      <c r="Y100" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8313,30 +8615,33 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q101" t="n">
-        <v>20.76</v>
+        <v>71</v>
       </c>
       <c r="R101" t="n">
+        <v>74</v>
+      </c>
+      <c r="S101" t="n">
         <v>32.2</v>
       </c>
-      <c r="S101" t="n">
+      <c r="T101" t="n">
         <v>38.2</v>
       </c>
-      <c r="T101" t="n">
+      <c r="U101" t="n">
         <v>31.4</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>51.8</v>
       </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
       <c r="W101" t="n">
-        <v>0.986735238189393</v>
-      </c>
-      <c r="X101" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0.958591776318657</v>
+      </c>
+      <c r="Y101" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8391,30 +8696,33 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>92.8</v>
+        <v>76</v>
       </c>
       <c r="Q102" t="n">
-        <v>20.68</v>
+        <v>71</v>
       </c>
       <c r="R102" t="n">
+        <v>74</v>
+      </c>
+      <c r="S102" t="n">
         <v>32.2</v>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="n">
         <v>39</v>
       </c>
-      <c r="T102" t="n">
+      <c r="U102" t="n">
         <v>31.6</v>
       </c>
-      <c r="U102" t="n">
+      <c r="V102" t="n">
         <v>51.6</v>
       </c>
-      <c r="V102" t="n">
-        <v>1</v>
-      </c>
       <c r="W102" t="n">
-        <v>0.9838708034535729</v>
-      </c>
-      <c r="X102" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1.102935495020107</v>
+      </c>
+      <c r="Y102" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8469,30 +8777,33 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q103" t="n">
-        <v>19.06</v>
+        <v>71</v>
       </c>
       <c r="R103" t="n">
+        <v>74</v>
+      </c>
+      <c r="S103" t="n">
         <v>32.6</v>
       </c>
-      <c r="S103" t="n">
+      <c r="T103" t="n">
         <v>39.2</v>
       </c>
-      <c r="T103" t="n">
+      <c r="U103" t="n">
         <v>31.4</v>
       </c>
-      <c r="U103" t="n">
+      <c r="V103" t="n">
         <v>50.8</v>
       </c>
-      <c r="V103" t="n">
-        <v>1</v>
-      </c>
       <c r="W103" t="n">
-        <v>1.003017644772493</v>
-      </c>
-      <c r="X103" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1.05717505989005</v>
+      </c>
+      <c r="Y103" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8547,30 +8858,33 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q104" t="n">
-        <v>18.06</v>
+        <v>71</v>
       </c>
       <c r="R104" t="n">
+        <v>74</v>
+      </c>
+      <c r="S104" t="n">
         <v>33</v>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="n">
         <v>39</v>
       </c>
-      <c r="T104" t="n">
+      <c r="U104" t="n">
         <v>31.4</v>
       </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>50.4</v>
       </c>
-      <c r="V104" t="n">
-        <v>1</v>
-      </c>
       <c r="W104" t="n">
-        <v>1.024481472917555</v>
-      </c>
-      <c r="X104" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X104" t="n">
+        <v>1.064409560847468</v>
+      </c>
+      <c r="Y104" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8625,30 +8939,33 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>99.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q105" t="n">
-        <v>17.26</v>
+        <v>71</v>
       </c>
       <c r="R105" t="n">
+        <v>74</v>
+      </c>
+      <c r="S105" t="n">
         <v>33</v>
       </c>
-      <c r="S105" t="n">
+      <c r="T105" t="n">
         <v>38.8</v>
       </c>
-      <c r="T105" t="n">
+      <c r="U105" t="n">
         <v>31</v>
       </c>
-      <c r="U105" t="n">
+      <c r="V105" t="n">
         <v>50</v>
       </c>
-      <c r="V105" t="n">
-        <v>1</v>
-      </c>
       <c r="W105" t="n">
-        <v>1.049486280890836</v>
-      </c>
-      <c r="X105" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X105" t="n">
+        <v>1.046289106998959</v>
+      </c>
+      <c r="Y105" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8703,30 +9020,33 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>100.4</v>
+        <v>76</v>
       </c>
       <c r="Q106" t="n">
-        <v>16.88</v>
+        <v>71</v>
       </c>
       <c r="R106" t="n">
+        <v>74</v>
+      </c>
+      <c r="S106" t="n">
         <v>33</v>
       </c>
-      <c r="S106" t="n">
+      <c r="T106" t="n">
         <v>38.6</v>
       </c>
-      <c r="T106" t="n">
+      <c r="U106" t="n">
         <v>31.2</v>
       </c>
-      <c r="U106" t="n">
+      <c r="V106" t="n">
         <v>50.2</v>
       </c>
-      <c r="V106" t="n">
-        <v>1</v>
-      </c>
       <c r="W106" t="n">
-        <v>0.9925664315522325</v>
-      </c>
-      <c r="X106" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1.053301385043504</v>
+      </c>
+      <c r="Y106" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8781,30 +9101,33 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>99.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q107" t="n">
-        <v>16.38</v>
+        <v>71</v>
       </c>
       <c r="R107" t="n">
+        <v>74</v>
+      </c>
+      <c r="S107" t="n">
         <v>32.6</v>
       </c>
-      <c r="S107" t="n">
+      <c r="T107" t="n">
         <v>38.6</v>
       </c>
-      <c r="T107" t="n">
+      <c r="U107" t="n">
         <v>31</v>
       </c>
-      <c r="U107" t="n">
+      <c r="V107" t="n">
         <v>50.6</v>
       </c>
-      <c r="V107" t="n">
-        <v>1</v>
-      </c>
       <c r="W107" t="n">
-        <v>1.000056403560745</v>
-      </c>
-      <c r="X107" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1.008238242169771</v>
+      </c>
+      <c r="Y107" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8859,30 +9182,33 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q108" t="n">
-        <v>16.58</v>
+        <v>71</v>
       </c>
       <c r="R108" t="n">
+        <v>74</v>
+      </c>
+      <c r="S108" t="n">
         <v>32</v>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="n">
         <v>38.6</v>
       </c>
-      <c r="T108" t="n">
+      <c r="U108" t="n">
         <v>31</v>
       </c>
-      <c r="U108" t="n">
+      <c r="V108" t="n">
         <v>51.2</v>
       </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
       <c r="W108" t="n">
-        <v>1.072317435351541</v>
-      </c>
-      <c r="X108" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0.9965225205337889</v>
+      </c>
+      <c r="Y108" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8937,32 +9263,35 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q109" t="n">
-        <v>16.78</v>
+        <v>71.2</v>
       </c>
       <c r="R109" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S109" t="n">
         <v>32</v>
       </c>
-      <c r="S109" t="n">
+      <c r="T109" t="n">
         <v>39.2</v>
       </c>
-      <c r="T109" t="n">
+      <c r="U109" t="n">
         <v>31</v>
       </c>
-      <c r="U109" t="n">
+      <c r="V109" t="n">
         <v>51.8</v>
       </c>
-      <c r="V109" t="n">
-        <v>1</v>
-      </c>
       <c r="W109" t="n">
-        <v>1.051940601935606</v>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1.429401645999592</v>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -9015,32 +9344,35 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q110" t="n">
-        <v>17.18</v>
+        <v>71.2</v>
       </c>
       <c r="R110" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S110" t="n">
         <v>32</v>
       </c>
-      <c r="S110" t="n">
+      <c r="T110" t="n">
         <v>39.4</v>
       </c>
-      <c r="T110" t="n">
+      <c r="U110" t="n">
         <v>31.2</v>
       </c>
-      <c r="U110" t="n">
+      <c r="V110" t="n">
         <v>52</v>
       </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
       <c r="W110" t="n">
-        <v>1.037849997649819</v>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X110" t="n">
+        <v>1.443090109536451</v>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -9093,32 +9425,35 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q111" t="n">
-        <v>17.3</v>
+        <v>71.2</v>
       </c>
       <c r="R111" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S111" t="n">
         <v>32.6</v>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="n">
         <v>39.6</v>
       </c>
-      <c r="T111" t="n">
+      <c r="U111" t="n">
         <v>31.4</v>
       </c>
-      <c r="U111" t="n">
+      <c r="V111" t="n">
         <v>51.8</v>
       </c>
-      <c r="V111" t="n">
-        <v>1</v>
-      </c>
       <c r="W111" t="n">
-        <v>1.040466701473195</v>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X111" t="n">
+        <v>1.387785721805088</v>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -9171,32 +9506,35 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q112" t="n">
-        <v>17.24</v>
+        <v>71.2</v>
       </c>
       <c r="R112" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S112" t="n">
         <v>33.6</v>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="n">
         <v>39.8</v>
       </c>
-      <c r="T112" t="n">
+      <c r="U112" t="n">
         <v>31.8</v>
       </c>
-      <c r="U112" t="n">
+      <c r="V112" t="n">
         <v>51.6</v>
       </c>
-      <c r="V112" t="n">
-        <v>1</v>
-      </c>
       <c r="W112" t="n">
-        <v>1.110628700796641</v>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1.515953644281285</v>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -9249,32 +9587,35 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q113" t="n">
-        <v>16.28</v>
+        <v>71.2</v>
       </c>
       <c r="R113" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S113" t="n">
         <v>33</v>
       </c>
-      <c r="S113" t="n">
+      <c r="T113" t="n">
         <v>38.6</v>
       </c>
-      <c r="T113" t="n">
+      <c r="U113" t="n">
         <v>32</v>
       </c>
-      <c r="U113" t="n">
+      <c r="V113" t="n">
         <v>52</v>
       </c>
-      <c r="V113" t="n">
-        <v>1</v>
-      </c>
       <c r="W113" t="n">
-        <v>1.080329266966353</v>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1.564693755193639</v>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -9327,30 +9668,33 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>92.8</v>
+        <v>76</v>
       </c>
       <c r="Q114" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R114" t="n">
+        <v>74</v>
+      </c>
+      <c r="S114" t="n">
         <v>32.2</v>
       </c>
-      <c r="S114" t="n">
+      <c r="T114" t="n">
         <v>37.6</v>
       </c>
-      <c r="T114" t="n">
+      <c r="U114" t="n">
         <v>31.8</v>
       </c>
-      <c r="U114" t="n">
+      <c r="V114" t="n">
         <v>52.2</v>
       </c>
-      <c r="V114" t="n">
-        <v>1</v>
-      </c>
       <c r="W114" t="n">
-        <v>0.9937058188582946</v>
-      </c>
-      <c r="X114" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1.013963080660625</v>
+      </c>
+      <c r="Y114" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9405,30 +9749,33 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q115" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R115" t="n">
+        <v>74</v>
+      </c>
+      <c r="S115" t="n">
         <v>31.4</v>
       </c>
-      <c r="S115" t="n">
+      <c r="T115" t="n">
         <v>36.8</v>
       </c>
-      <c r="T115" t="n">
+      <c r="U115" t="n">
         <v>31.6</v>
       </c>
-      <c r="U115" t="n">
+      <c r="V115" t="n">
         <v>52.8</v>
       </c>
-      <c r="V115" t="n">
-        <v>1</v>
-      </c>
       <c r="W115" t="n">
-        <v>0.9910287281736829</v>
-      </c>
-      <c r="X115" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X115" t="n">
+        <v>1.036434318449386</v>
+      </c>
+      <c r="Y115" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9483,30 +9830,33 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q116" t="n">
-        <v>17.28</v>
+        <v>71</v>
       </c>
       <c r="R116" t="n">
+        <v>74</v>
+      </c>
+      <c r="S116" t="n">
         <v>30.6</v>
       </c>
-      <c r="S116" t="n">
+      <c r="T116" t="n">
         <v>36.4</v>
       </c>
-      <c r="T116" t="n">
+      <c r="U116" t="n">
         <v>31.8</v>
       </c>
-      <c r="U116" t="n">
+      <c r="V116" t="n">
         <v>53.6</v>
       </c>
-      <c r="V116" t="n">
-        <v>1</v>
-      </c>
       <c r="W116" t="n">
-        <v>0.9959587291649472</v>
-      </c>
-      <c r="X116" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X116" t="n">
+        <v>1.08898826327581</v>
+      </c>
+      <c r="Y116" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9561,30 +9911,33 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q117" t="n">
-        <v>17.58</v>
+        <v>71</v>
       </c>
       <c r="R117" t="n">
+        <v>74</v>
+      </c>
+      <c r="S117" t="n">
         <v>29.8</v>
       </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>36</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>31.8</v>
       </c>
-      <c r="U117" t="n">
+      <c r="V117" t="n">
         <v>54.4</v>
       </c>
-      <c r="V117" t="n">
-        <v>1</v>
-      </c>
       <c r="W117" t="n">
-        <v>1.022557588700867</v>
-      </c>
-      <c r="X117" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X117" t="n">
+        <v>1.173326279099606</v>
+      </c>
+      <c r="Y117" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9639,30 +9992,33 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q118" t="n">
-        <v>17.62</v>
+        <v>71</v>
       </c>
       <c r="R118" t="n">
+        <v>74</v>
+      </c>
+      <c r="S118" t="n">
         <v>30.8</v>
       </c>
-      <c r="S118" t="n">
+      <c r="T118" t="n">
         <v>37</v>
       </c>
-      <c r="T118" t="n">
+      <c r="U118" t="n">
         <v>31.8</v>
       </c>
-      <c r="U118" t="n">
+      <c r="V118" t="n">
         <v>54.4</v>
       </c>
-      <c r="V118" t="n">
-        <v>1</v>
-      </c>
       <c r="W118" t="n">
-        <v>1.038671449910882</v>
-      </c>
-      <c r="X118" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1.169660421695496</v>
+      </c>
+      <c r="Y118" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9717,30 +10073,33 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q119" t="n">
-        <v>16.22</v>
+        <v>71</v>
       </c>
       <c r="R119" t="n">
+        <v>74</v>
+      </c>
+      <c r="S119" t="n">
         <v>30.4</v>
       </c>
-      <c r="S119" t="n">
+      <c r="T119" t="n">
         <v>36.4</v>
       </c>
-      <c r="T119" t="n">
+      <c r="U119" t="n">
         <v>31.6</v>
       </c>
-      <c r="U119" t="n">
+      <c r="V119" t="n">
         <v>53.4</v>
       </c>
-      <c r="V119" t="n">
-        <v>1</v>
-      </c>
       <c r="W119" t="n">
-        <v>1.039168860712207</v>
-      </c>
-      <c r="X119" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1.089687761018839</v>
+      </c>
+      <c r="Y119" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9795,30 +10154,33 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q120" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R120" t="n">
+        <v>74</v>
+      </c>
+      <c r="S120" t="n">
         <v>30</v>
       </c>
-      <c r="S120" t="n">
+      <c r="T120" t="n">
         <v>36.6</v>
       </c>
-      <c r="T120" t="n">
+      <c r="U120" t="n">
         <v>31.8</v>
       </c>
-      <c r="U120" t="n">
+      <c r="V120" t="n">
         <v>53.4</v>
       </c>
-      <c r="V120" t="n">
-        <v>1</v>
-      </c>
       <c r="W120" t="n">
-        <v>1.034507581631495</v>
-      </c>
-      <c r="X120" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1.113305929024169</v>
+      </c>
+      <c r="Y120" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9873,30 +10235,33 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q121" t="n">
-        <v>17.58</v>
+        <v>71</v>
       </c>
       <c r="R121" t="n">
+        <v>74</v>
+      </c>
+      <c r="S121" t="n">
         <v>29</v>
       </c>
-      <c r="S121" t="n">
+      <c r="T121" t="n">
         <v>36.4</v>
       </c>
-      <c r="T121" t="n">
+      <c r="U121" t="n">
         <v>31.6</v>
       </c>
-      <c r="U121" t="n">
+      <c r="V121" t="n">
         <v>53.6</v>
       </c>
-      <c r="V121" t="n">
-        <v>1</v>
-      </c>
       <c r="W121" t="n">
-        <v>1.028432314315785</v>
-      </c>
-      <c r="X121" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X121" t="n">
+        <v>1.142559128372092</v>
+      </c>
+      <c r="Y121" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -9951,30 +10316,33 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q122" t="n">
-        <v>18.78</v>
+        <v>71</v>
       </c>
       <c r="R122" t="n">
+        <v>74</v>
+      </c>
+      <c r="S122" t="n">
         <v>29</v>
       </c>
-      <c r="S122" t="n">
+      <c r="T122" t="n">
         <v>36.4</v>
       </c>
-      <c r="T122" t="n">
+      <c r="U122" t="n">
         <v>31.8</v>
       </c>
-      <c r="U122" t="n">
+      <c r="V122" t="n">
         <v>53.6</v>
       </c>
-      <c r="V122" t="n">
-        <v>1</v>
-      </c>
       <c r="W122" t="n">
-        <v>1.033128897663117</v>
-      </c>
-      <c r="X122" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X122" t="n">
+        <v>1.14637628392005</v>
+      </c>
+      <c r="Y122" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10029,30 +10397,33 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q123" t="n">
-        <v>19.42</v>
+        <v>71</v>
       </c>
       <c r="R123" t="n">
+        <v>74</v>
+      </c>
+      <c r="S123" t="n">
         <v>28.2</v>
       </c>
-      <c r="S123" t="n">
+      <c r="T123" t="n">
         <v>35.6</v>
       </c>
-      <c r="T123" t="n">
+      <c r="U123" t="n">
         <v>31.6</v>
       </c>
-      <c r="U123" t="n">
+      <c r="V123" t="n">
         <v>53.6</v>
       </c>
-      <c r="V123" t="n">
-        <v>1</v>
-      </c>
       <c r="W123" t="n">
-        <v>1.042287103409046</v>
-      </c>
-      <c r="X123" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1.209225764362621</v>
+      </c>
+      <c r="Y123" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10107,30 +10478,33 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q124" t="n">
-        <v>20.38</v>
+        <v>71</v>
       </c>
       <c r="R124" t="n">
+        <v>74</v>
+      </c>
+      <c r="S124" t="n">
         <v>29</v>
       </c>
-      <c r="S124" t="n">
+      <c r="T124" t="n">
         <v>36.8</v>
       </c>
-      <c r="T124" t="n">
+      <c r="U124" t="n">
         <v>32</v>
       </c>
-      <c r="U124" t="n">
+      <c r="V124" t="n">
         <v>54.6</v>
       </c>
-      <c r="V124" t="n">
-        <v>1</v>
-      </c>
       <c r="W124" t="n">
-        <v>1.170620783479389</v>
-      </c>
-      <c r="X124" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X124" t="n">
+        <v>1.203740509724814</v>
+      </c>
+      <c r="Y124" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10185,30 +10559,33 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>94.2</v>
+        <v>76</v>
       </c>
       <c r="Q125" t="n">
-        <v>19.72</v>
+        <v>71</v>
       </c>
       <c r="R125" t="n">
+        <v>74</v>
+      </c>
+      <c r="S125" t="n">
         <v>29.8</v>
       </c>
-      <c r="S125" t="n">
+      <c r="T125" t="n">
         <v>37</v>
       </c>
-      <c r="T125" t="n">
+      <c r="U125" t="n">
         <v>31.6</v>
       </c>
-      <c r="U125" t="n">
+      <c r="V125" t="n">
         <v>53.8</v>
       </c>
-      <c r="V125" t="n">
-        <v>1</v>
-      </c>
       <c r="W125" t="n">
-        <v>1.016096182879327</v>
-      </c>
-      <c r="X125" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X125" t="n">
+        <v>1.155460544309354</v>
+      </c>
+      <c r="Y125" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10263,30 +10640,33 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q126" t="n">
-        <v>18.22</v>
+        <v>71</v>
       </c>
       <c r="R126" t="n">
+        <v>74</v>
+      </c>
+      <c r="S126" t="n">
         <v>30.6</v>
       </c>
-      <c r="S126" t="n">
+      <c r="T126" t="n">
         <v>37.2</v>
       </c>
-      <c r="T126" t="n">
+      <c r="U126" t="n">
         <v>31.2</v>
       </c>
-      <c r="U126" t="n">
+      <c r="V126" t="n">
         <v>53</v>
       </c>
-      <c r="V126" t="n">
-        <v>1</v>
-      </c>
       <c r="W126" t="n">
-        <v>0.9991386485875022</v>
-      </c>
-      <c r="X126" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1.039820908350646</v>
+      </c>
+      <c r="Y126" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10341,30 +10721,33 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q127" t="n">
-        <v>16.92</v>
+        <v>71</v>
       </c>
       <c r="R127" t="n">
+        <v>74</v>
+      </c>
+      <c r="S127" t="n">
         <v>30.2</v>
       </c>
-      <c r="S127" t="n">
+      <c r="T127" t="n">
         <v>36.8</v>
       </c>
-      <c r="T127" t="n">
+      <c r="U127" t="n">
         <v>30.4</v>
       </c>
-      <c r="U127" t="n">
+      <c r="V127" t="n">
         <v>52.4</v>
       </c>
-      <c r="V127" t="n">
-        <v>1</v>
-      </c>
       <c r="W127" t="n">
-        <v>0.9988994307687291</v>
-      </c>
-      <c r="X127" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1.089637435257977</v>
+      </c>
+      <c r="Y127" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10419,30 +10802,33 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q128" t="n">
-        <v>17.2</v>
+        <v>71</v>
       </c>
       <c r="R128" t="n">
+        <v>74</v>
+      </c>
+      <c r="S128" t="n">
         <v>30</v>
       </c>
-      <c r="S128" t="n">
+      <c r="T128" t="n">
         <v>36.4</v>
       </c>
-      <c r="T128" t="n">
+      <c r="U128" t="n">
         <v>30</v>
       </c>
-      <c r="U128" t="n">
+      <c r="V128" t="n">
         <v>52.4</v>
       </c>
-      <c r="V128" t="n">
-        <v>1</v>
-      </c>
       <c r="W128" t="n">
-        <v>1.012929416576822</v>
-      </c>
-      <c r="X128" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1.169053291900002</v>
+      </c>
+      <c r="Y128" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10497,30 +10883,33 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>89.2</v>
+        <v>76</v>
       </c>
       <c r="Q129" t="n">
-        <v>17.92</v>
+        <v>71</v>
       </c>
       <c r="R129" t="n">
+        <v>74</v>
+      </c>
+      <c r="S129" t="n">
         <v>29.8</v>
       </c>
-      <c r="S129" t="n">
+      <c r="T129" t="n">
         <v>36.6</v>
       </c>
-      <c r="T129" t="n">
+      <c r="U129" t="n">
         <v>29.6</v>
       </c>
-      <c r="U129" t="n">
+      <c r="V129" t="n">
         <v>52.2</v>
       </c>
-      <c r="V129" t="n">
-        <v>1</v>
-      </c>
       <c r="W129" t="n">
-        <v>1.130044031922712</v>
-      </c>
-      <c r="X129" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X129" t="n">
+        <v>1.221010999548296</v>
+      </c>
+      <c r="Y129" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10575,32 +10964,35 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q130" t="n">
-        <v>17.74</v>
+        <v>70.8</v>
       </c>
       <c r="R130" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S130" t="n">
         <v>30.2</v>
       </c>
-      <c r="S130" t="n">
+      <c r="T130" t="n">
         <v>36.6</v>
       </c>
-      <c r="T130" t="n">
+      <c r="U130" t="n">
         <v>29.6</v>
       </c>
-      <c r="U130" t="n">
+      <c r="V130" t="n">
         <v>52.6</v>
       </c>
-      <c r="V130" t="n">
-        <v>1</v>
-      </c>
       <c r="W130" t="n">
-        <v>1.02227862704151</v>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X130" t="n">
+        <v>1.922514720485564</v>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10653,32 +11045,35 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>90.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q131" t="n">
-        <v>17.44</v>
+        <v>70.8</v>
       </c>
       <c r="R131" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S131" t="n">
         <v>29</v>
       </c>
-      <c r="S131" t="n">
+      <c r="T131" t="n">
         <v>35.6</v>
       </c>
-      <c r="T131" t="n">
+      <c r="U131" t="n">
         <v>29.2</v>
       </c>
-      <c r="U131" t="n">
+      <c r="V131" t="n">
         <v>52.4</v>
       </c>
-      <c r="V131" t="n">
-        <v>1</v>
-      </c>
       <c r="W131" t="n">
-        <v>1.031017887273626</v>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X131" t="n">
+        <v>1.522998146892889</v>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -10731,32 +11126,35 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>92.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q132" t="n">
-        <v>17.46</v>
+        <v>70.8</v>
       </c>
       <c r="R132" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S132" t="n">
         <v>28.8</v>
       </c>
-      <c r="S132" t="n">
+      <c r="T132" t="n">
         <v>35.8</v>
       </c>
-      <c r="T132" t="n">
+      <c r="U132" t="n">
         <v>29.2</v>
       </c>
-      <c r="U132" t="n">
+      <c r="V132" t="n">
         <v>52.6</v>
       </c>
-      <c r="V132" t="n">
-        <v>1</v>
-      </c>
       <c r="W132" t="n">
-        <v>1.010096624687965</v>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X132" t="n">
+        <v>1.565266883372762</v>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -10809,32 +11207,35 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>92.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q133" t="n">
-        <v>17.74</v>
+        <v>70.8</v>
       </c>
       <c r="R133" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S133" t="n">
         <v>29.2</v>
       </c>
-      <c r="S133" t="n">
+      <c r="T133" t="n">
         <v>36.8</v>
       </c>
-      <c r="T133" t="n">
+      <c r="U133" t="n">
         <v>29.2</v>
       </c>
-      <c r="U133" t="n">
+      <c r="V133" t="n">
         <v>52</v>
       </c>
-      <c r="V133" t="n">
-        <v>1</v>
-      </c>
       <c r="W133" t="n">
-        <v>0.981790271763483</v>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1.779015918919383</v>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10887,32 +11288,35 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>92.2</v>
+        <v>75.8</v>
       </c>
       <c r="Q134" t="n">
-        <v>17.5</v>
+        <v>70.8</v>
       </c>
       <c r="R134" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S134" t="n">
         <v>29</v>
       </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
         <v>36.4</v>
       </c>
-      <c r="T134" t="n">
+      <c r="U134" t="n">
         <v>29</v>
       </c>
-      <c r="U134" t="n">
+      <c r="V134" t="n">
         <v>51.4</v>
       </c>
-      <c r="V134" t="n">
-        <v>1</v>
-      </c>
       <c r="W134" t="n">
-        <v>1.00469317881225</v>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X134" t="n">
+        <v>1.586011635660412</v>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -10965,32 +11369,35 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="Q135" t="n">
-        <v>16.88</v>
+        <v>71</v>
       </c>
       <c r="R135" t="n">
+        <v>74</v>
+      </c>
+      <c r="S135" t="n">
         <v>28.6</v>
       </c>
-      <c r="S135" t="n">
+      <c r="T135" t="n">
         <v>36.2</v>
       </c>
-      <c r="T135" t="n">
+      <c r="U135" t="n">
         <v>29.2</v>
       </c>
-      <c r="U135" t="n">
+      <c r="V135" t="n">
         <v>51</v>
       </c>
-      <c r="V135" t="n">
-        <v>1</v>
-      </c>
       <c r="W135" t="n">
-        <v>1.002006073606567</v>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1.350478334969738</v>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11043,30 +11450,33 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>93.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q136" t="n">
-        <v>16.98</v>
+        <v>71</v>
       </c>
       <c r="R136" t="n">
+        <v>74</v>
+      </c>
+      <c r="S136" t="n">
         <v>30.2</v>
       </c>
-      <c r="S136" t="n">
+      <c r="T136" t="n">
         <v>36.4</v>
       </c>
-      <c r="T136" t="n">
+      <c r="U136" t="n">
         <v>23.84</v>
       </c>
-      <c r="U136" t="n">
+      <c r="V136" t="n">
         <v>51.2</v>
       </c>
-      <c r="V136" t="n">
+      <c r="W136" t="n">
         <v>-1</v>
       </c>
-      <c r="W136" t="n">
-        <v>1.55620130003232</v>
-      </c>
-      <c r="X136" t="inlineStr">
+      <c r="X136" t="n">
+        <v>2.928100598745822</v>
+      </c>
+      <c r="Y136" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -11121,30 +11531,33 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>94.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q137" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R137" t="n">
+        <v>74</v>
+      </c>
+      <c r="S137" t="n">
         <v>30</v>
       </c>
-      <c r="S137" t="n">
+      <c r="T137" t="n">
         <v>35.8</v>
       </c>
-      <c r="T137" t="n">
+      <c r="U137" t="n">
         <v>23.64</v>
       </c>
-      <c r="U137" t="n">
+      <c r="V137" t="n">
         <v>51</v>
       </c>
-      <c r="V137" t="n">
+      <c r="W137" t="n">
         <v>-1</v>
       </c>
-      <c r="W137" t="n">
-        <v>1.637695040469363</v>
-      </c>
-      <c r="X137" t="inlineStr">
+      <c r="X137" t="n">
+        <v>2.79767179447176</v>
+      </c>
+      <c r="Y137" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -11199,30 +11612,33 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>95.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>14.58</v>
+        <v>71</v>
       </c>
       <c r="R138" t="n">
+        <v>74</v>
+      </c>
+      <c r="S138" t="n">
         <v>30</v>
       </c>
-      <c r="S138" t="n">
+      <c r="T138" t="n">
         <v>34.8</v>
       </c>
-      <c r="T138" t="n">
+      <c r="U138" t="n">
         <v>23.64</v>
       </c>
-      <c r="U138" t="n">
+      <c r="V138" t="n">
         <v>51.2</v>
       </c>
-      <c r="V138" t="n">
+      <c r="W138" t="n">
         <v>-1</v>
       </c>
-      <c r="W138" t="n">
-        <v>1.787956976941173</v>
-      </c>
-      <c r="X138" t="inlineStr">
+      <c r="X138" t="n">
+        <v>2.68816750217034</v>
+      </c>
+      <c r="Y138" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -11277,30 +11693,33 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q139" t="n">
-        <v>14.32</v>
+        <v>71</v>
       </c>
       <c r="R139" t="n">
+        <v>74</v>
+      </c>
+      <c r="S139" t="n">
         <v>30</v>
       </c>
-      <c r="S139" t="n">
+      <c r="T139" t="n">
         <v>34.6</v>
       </c>
-      <c r="T139" t="n">
+      <c r="U139" t="n">
         <v>23.64</v>
       </c>
-      <c r="U139" t="n">
+      <c r="V139" t="n">
         <v>51.4</v>
       </c>
-      <c r="V139" t="n">
+      <c r="W139" t="n">
         <v>-1</v>
       </c>
-      <c r="W139" t="n">
-        <v>1.762893573104774</v>
-      </c>
-      <c r="X139" t="inlineStr">
+      <c r="X139" t="n">
+        <v>2.66191074879543</v>
+      </c>
+      <c r="Y139" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -11355,30 +11774,33 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q140" t="n">
-        <v>15.7</v>
+        <v>71</v>
       </c>
       <c r="R140" t="n">
+        <v>74</v>
+      </c>
+      <c r="S140" t="n">
         <v>29.6</v>
       </c>
-      <c r="S140" t="n">
+      <c r="T140" t="n">
         <v>34.4</v>
       </c>
-      <c r="T140" t="n">
+      <c r="U140" t="n">
         <v>23.24</v>
       </c>
-      <c r="U140" t="n">
+      <c r="V140" t="n">
         <v>51.6</v>
       </c>
-      <c r="V140" t="n">
+      <c r="W140" t="n">
         <v>-1</v>
       </c>
-      <c r="W140" t="n">
-        <v>1.756404605490399</v>
-      </c>
-      <c r="X140" t="inlineStr">
+      <c r="X140" t="n">
+        <v>2.701408361458676</v>
+      </c>
+      <c r="Y140" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -11433,32 +11855,35 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q141" t="n">
-        <v>16.22</v>
+        <v>71</v>
       </c>
       <c r="R141" t="n">
+        <v>74</v>
+      </c>
+      <c r="S141" t="n">
         <v>29.4</v>
       </c>
-      <c r="S141" t="n">
+      <c r="T141" t="n">
         <v>35.2</v>
       </c>
-      <c r="T141" t="n">
+      <c r="U141" t="n">
         <v>29</v>
       </c>
-      <c r="U141" t="n">
+      <c r="V141" t="n">
         <v>51.8</v>
       </c>
-      <c r="V141" t="n">
-        <v>1</v>
-      </c>
       <c r="W141" t="n">
-        <v>1.12706487296785</v>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1.326371335347967</v>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11511,32 +11936,35 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q142" t="n">
-        <v>17.12</v>
+        <v>71</v>
       </c>
       <c r="R142" t="n">
+        <v>74</v>
+      </c>
+      <c r="S142" t="n">
         <v>29.8</v>
       </c>
-      <c r="S142" t="n">
+      <c r="T142" t="n">
         <v>34.8</v>
       </c>
-      <c r="T142" t="n">
+      <c r="U142" t="n">
         <v>29.2</v>
       </c>
-      <c r="U142" t="n">
+      <c r="V142" t="n">
         <v>52</v>
       </c>
-      <c r="V142" t="n">
-        <v>1</v>
-      </c>
       <c r="W142" t="n">
-        <v>1.079787069469966</v>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>1.30966332945921</v>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11589,32 +12017,35 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>94.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q143" t="n">
-        <v>18.06</v>
+        <v>71</v>
       </c>
       <c r="R143" t="n">
+        <v>74</v>
+      </c>
+      <c r="S143" t="n">
         <v>29.4</v>
       </c>
-      <c r="S143" t="n">
+      <c r="T143" t="n">
         <v>34.8</v>
       </c>
-      <c r="T143" t="n">
+      <c r="U143" t="n">
         <v>29.2</v>
       </c>
-      <c r="U143" t="n">
+      <c r="V143" t="n">
         <v>52</v>
       </c>
-      <c r="V143" t="n">
-        <v>1</v>
-      </c>
       <c r="W143" t="n">
-        <v>1.066671313356416</v>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>1.308939769963561</v>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11667,32 +12098,35 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q144" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R144" t="n">
+        <v>74</v>
+      </c>
+      <c r="S144" t="n">
         <v>28.6</v>
       </c>
-      <c r="S144" t="n">
+      <c r="T144" t="n">
         <v>34</v>
       </c>
-      <c r="T144" t="n">
+      <c r="U144" t="n">
         <v>29.2</v>
       </c>
-      <c r="U144" t="n">
+      <c r="V144" t="n">
         <v>52</v>
       </c>
-      <c r="V144" t="n">
-        <v>1</v>
-      </c>
       <c r="W144" t="n">
-        <v>1.028809340660847</v>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X144" t="n">
+        <v>1.376201427540576</v>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11745,32 +12179,35 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>91.2</v>
+        <v>76</v>
       </c>
       <c r="Q145" t="n">
-        <v>16.5</v>
+        <v>71</v>
       </c>
       <c r="R145" t="n">
+        <v>74</v>
+      </c>
+      <c r="S145" t="n">
         <v>27.8</v>
       </c>
-      <c r="S145" t="n">
+      <c r="T145" t="n">
         <v>33.2</v>
       </c>
-      <c r="T145" t="n">
+      <c r="U145" t="n">
         <v>29.2</v>
       </c>
-      <c r="U145" t="n">
+      <c r="V145" t="n">
         <v>52</v>
       </c>
-      <c r="V145" t="n">
-        <v>1</v>
-      </c>
       <c r="W145" t="n">
-        <v>1.123269432616772</v>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X145" t="n">
+        <v>1.524489532491182</v>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11823,32 +12260,35 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q146" t="n">
-        <v>16.98</v>
+        <v>71</v>
       </c>
       <c r="R146" t="n">
+        <v>74</v>
+      </c>
+      <c r="S146" t="n">
         <v>27.6</v>
       </c>
-      <c r="S146" t="n">
+      <c r="T146" t="n">
         <v>33</v>
       </c>
-      <c r="T146" t="n">
+      <c r="U146" t="n">
         <v>29.4</v>
       </c>
-      <c r="U146" t="n">
+      <c r="V146" t="n">
         <v>51.8</v>
       </c>
-      <c r="V146" t="n">
-        <v>1</v>
-      </c>
       <c r="W146" t="n">
-        <v>1.1312696849204</v>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X146" t="n">
+        <v>1.587930175572562</v>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11901,32 +12341,35 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q147" t="n">
-        <v>16.72</v>
+        <v>71</v>
       </c>
       <c r="R147" t="n">
+        <v>74</v>
+      </c>
+      <c r="S147" t="n">
         <v>28</v>
       </c>
-      <c r="S147" t="n">
+      <c r="T147" t="n">
         <v>34</v>
       </c>
-      <c r="T147" t="n">
+      <c r="U147" t="n">
         <v>29.8</v>
       </c>
-      <c r="U147" t="n">
+      <c r="V147" t="n">
         <v>51.6</v>
       </c>
-      <c r="V147" t="n">
-        <v>1</v>
-      </c>
       <c r="W147" t="n">
-        <v>1.04415064451947</v>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X147" t="n">
+        <v>1.36679867798341</v>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -11979,30 +12422,33 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>95.8</v>
+        <v>76</v>
       </c>
       <c r="Q148" t="n">
-        <v>16.18</v>
+        <v>71</v>
       </c>
       <c r="R148" t="n">
+        <v>74</v>
+      </c>
+      <c r="S148" t="n">
         <v>29</v>
       </c>
-      <c r="S148" t="n">
+      <c r="T148" t="n">
         <v>35</v>
       </c>
-      <c r="T148" t="n">
+      <c r="U148" t="n">
         <v>30.2</v>
       </c>
-      <c r="U148" t="n">
+      <c r="V148" t="n">
         <v>51.4</v>
       </c>
-      <c r="V148" t="n">
-        <v>1</v>
-      </c>
       <c r="W148" t="n">
-        <v>1.100301000497047</v>
-      </c>
-      <c r="X148" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X148" t="n">
+        <v>1.209818933446486</v>
+      </c>
+      <c r="Y148" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12057,30 +12503,33 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>100.4</v>
+        <v>76</v>
       </c>
       <c r="Q149" t="n">
-        <v>15.58</v>
+        <v>71</v>
       </c>
       <c r="R149" t="n">
+        <v>74</v>
+      </c>
+      <c r="S149" t="n">
         <v>30.2</v>
       </c>
-      <c r="S149" t="n">
+      <c r="T149" t="n">
         <v>35.8</v>
       </c>
-      <c r="T149" t="n">
+      <c r="U149" t="n">
         <v>30.6</v>
       </c>
-      <c r="U149" t="n">
+      <c r="V149" t="n">
         <v>51.2</v>
       </c>
-      <c r="V149" t="n">
-        <v>1</v>
-      </c>
       <c r="W149" t="n">
-        <v>1.00060492256173</v>
-      </c>
-      <c r="X149" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X149" t="n">
+        <v>1.124060216744027</v>
+      </c>
+      <c r="Y149" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12135,30 +12584,33 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>102.8</v>
+        <v>76</v>
       </c>
       <c r="Q150" t="n">
-        <v>14.26</v>
+        <v>71</v>
       </c>
       <c r="R150" t="n">
+        <v>74</v>
+      </c>
+      <c r="S150" t="n">
         <v>31.2</v>
       </c>
-      <c r="S150" t="n">
+      <c r="T150" t="n">
         <v>36.6</v>
       </c>
-      <c r="T150" t="n">
+      <c r="U150" t="n">
         <v>30.8</v>
       </c>
-      <c r="U150" t="n">
+      <c r="V150" t="n">
         <v>51.4</v>
       </c>
-      <c r="V150" t="n">
-        <v>1</v>
-      </c>
       <c r="W150" t="n">
-        <v>1.069373402417681</v>
-      </c>
-      <c r="X150" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X150" t="n">
+        <v>1.065458345750095</v>
+      </c>
+      <c r="Y150" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12213,30 +12665,33 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q151" t="n">
-        <v>14.26</v>
+        <v>71</v>
       </c>
       <c r="R151" t="n">
+        <v>74</v>
+      </c>
+      <c r="S151" t="n">
         <v>31</v>
       </c>
-      <c r="S151" t="n">
+      <c r="T151" t="n">
         <v>36.4</v>
       </c>
-      <c r="T151" t="n">
+      <c r="U151" t="n">
         <v>30.6</v>
       </c>
-      <c r="U151" t="n">
+      <c r="V151" t="n">
         <v>51.8</v>
       </c>
-      <c r="V151" t="n">
-        <v>1</v>
-      </c>
       <c r="W151" t="n">
-        <v>1.033444806834097</v>
-      </c>
-      <c r="X151" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X151" t="n">
+        <v>1.09724932155461</v>
+      </c>
+      <c r="Y151" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12291,30 +12746,33 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>99.8</v>
+        <v>76</v>
       </c>
       <c r="Q152" t="n">
-        <v>15.66</v>
+        <v>71</v>
       </c>
       <c r="R152" t="n">
+        <v>74</v>
+      </c>
+      <c r="S152" t="n">
         <v>31</v>
       </c>
-      <c r="S152" t="n">
+      <c r="T152" t="n">
         <v>36.2</v>
       </c>
-      <c r="T152" t="n">
+      <c r="U152" t="n">
         <v>30.6</v>
       </c>
-      <c r="U152" t="n">
+      <c r="V152" t="n">
         <v>52</v>
       </c>
-      <c r="V152" t="n">
-        <v>1</v>
-      </c>
       <c r="W152" t="n">
-        <v>1.009821071970197</v>
-      </c>
-      <c r="X152" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X152" t="n">
+        <v>1.106123043610095</v>
+      </c>
+      <c r="Y152" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12369,30 +12827,33 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>99.2</v>
+        <v>76</v>
       </c>
       <c r="Q153" t="n">
-        <v>16.5</v>
+        <v>71</v>
       </c>
       <c r="R153" t="n">
+        <v>74</v>
+      </c>
+      <c r="S153" t="n">
         <v>31.2</v>
       </c>
-      <c r="S153" t="n">
+      <c r="T153" t="n">
         <v>36.4</v>
       </c>
-      <c r="T153" t="n">
+      <c r="U153" t="n">
         <v>30.6</v>
       </c>
-      <c r="U153" t="n">
+      <c r="V153" t="n">
         <v>52</v>
       </c>
-      <c r="V153" t="n">
-        <v>1</v>
-      </c>
       <c r="W153" t="n">
-        <v>1.032137983610906</v>
-      </c>
-      <c r="X153" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X153" t="n">
+        <v>1.080951063263929</v>
+      </c>
+      <c r="Y153" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12447,30 +12908,33 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q154" t="n">
-        <v>17.3</v>
+        <v>71</v>
       </c>
       <c r="R154" t="n">
+        <v>74</v>
+      </c>
+      <c r="S154" t="n">
         <v>31</v>
       </c>
-      <c r="S154" t="n">
+      <c r="T154" t="n">
         <v>36.8</v>
       </c>
-      <c r="T154" t="n">
+      <c r="U154" t="n">
         <v>30.8</v>
       </c>
-      <c r="U154" t="n">
+      <c r="V154" t="n">
         <v>52.2</v>
       </c>
-      <c r="V154" t="n">
-        <v>1</v>
-      </c>
       <c r="W154" t="n">
-        <v>1.040159470663071</v>
-      </c>
-      <c r="X154" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0.9999587818474392</v>
+      </c>
+      <c r="Y154" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12525,30 +12989,33 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q155" t="n">
-        <v>17.52</v>
+        <v>71</v>
       </c>
       <c r="R155" t="n">
+        <v>74</v>
+      </c>
+      <c r="S155" t="n">
         <v>31</v>
       </c>
-      <c r="S155" t="n">
+      <c r="T155" t="n">
         <v>37.2</v>
       </c>
-      <c r="T155" t="n">
+      <c r="U155" t="n">
         <v>31.2</v>
       </c>
-      <c r="U155" t="n">
+      <c r="V155" t="n">
         <v>52</v>
       </c>
-      <c r="V155" t="n">
-        <v>1</v>
-      </c>
       <c r="W155" t="n">
-        <v>1.062666724276766</v>
-      </c>
-      <c r="X155" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0.99453855485255</v>
+      </c>
+      <c r="Y155" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12603,30 +13070,33 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q156" t="n">
-        <v>18.04</v>
+        <v>71</v>
       </c>
       <c r="R156" t="n">
+        <v>74</v>
+      </c>
+      <c r="S156" t="n">
         <v>30.8</v>
       </c>
-      <c r="S156" t="n">
+      <c r="T156" t="n">
         <v>37.6</v>
       </c>
-      <c r="T156" t="n">
+      <c r="U156" t="n">
         <v>31.4</v>
       </c>
-      <c r="U156" t="n">
+      <c r="V156" t="n">
         <v>51.8</v>
       </c>
-      <c r="V156" t="n">
-        <v>1</v>
-      </c>
       <c r="W156" t="n">
-        <v>1.050525030847476</v>
-      </c>
-      <c r="X156" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X156" t="n">
+        <v>1.007164116826828</v>
+      </c>
+      <c r="Y156" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12681,30 +13151,33 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q157" t="n">
-        <v>18.3</v>
+        <v>71</v>
       </c>
       <c r="R157" t="n">
+        <v>74</v>
+      </c>
+      <c r="S157" t="n">
         <v>30.8</v>
       </c>
-      <c r="S157" t="n">
+      <c r="T157" t="n">
         <v>38</v>
       </c>
-      <c r="T157" t="n">
+      <c r="U157" t="n">
         <v>31.2</v>
       </c>
-      <c r="U157" t="n">
+      <c r="V157" t="n">
         <v>51.8</v>
       </c>
-      <c r="V157" t="n">
-        <v>1</v>
-      </c>
       <c r="W157" t="n">
-        <v>1.018217535551518</v>
-      </c>
-      <c r="X157" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0.9963754740041534</v>
+      </c>
+      <c r="Y157" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12759,30 +13232,33 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q158" t="n">
-        <v>18.48</v>
+        <v>71</v>
       </c>
       <c r="R158" t="n">
+        <v>74</v>
+      </c>
+      <c r="S158" t="n">
         <v>30.8</v>
       </c>
-      <c r="S158" t="n">
+      <c r="T158" t="n">
         <v>38</v>
       </c>
-      <c r="T158" t="n">
+      <c r="U158" t="n">
         <v>31.2</v>
       </c>
-      <c r="U158" t="n">
+      <c r="V158" t="n">
         <v>52.2</v>
       </c>
-      <c r="V158" t="n">
-        <v>1</v>
-      </c>
       <c r="W158" t="n">
-        <v>1.004588140667585</v>
-      </c>
-      <c r="X158" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0.9932278418178679</v>
+      </c>
+      <c r="Y158" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12837,30 +13313,33 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q159" t="n">
-        <v>18.5</v>
+        <v>71</v>
       </c>
       <c r="R159" t="n">
+        <v>74</v>
+      </c>
+      <c r="S159" t="n">
         <v>31</v>
       </c>
-      <c r="S159" t="n">
+      <c r="T159" t="n">
         <v>37.8</v>
       </c>
-      <c r="T159" t="n">
+      <c r="U159" t="n">
         <v>30.8</v>
       </c>
-      <c r="U159" t="n">
+      <c r="V159" t="n">
         <v>52.2</v>
       </c>
-      <c r="V159" t="n">
-        <v>1</v>
-      </c>
       <c r="W159" t="n">
-        <v>1.002992640844016</v>
-      </c>
-      <c r="X159" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0.9787465011303651</v>
+      </c>
+      <c r="Y159" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -12915,32 +13394,35 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q160" t="n">
-        <v>18.6</v>
+        <v>71</v>
       </c>
       <c r="R160" t="n">
+        <v>74</v>
+      </c>
+      <c r="S160" t="n">
         <v>30.4</v>
       </c>
-      <c r="S160" t="n">
+      <c r="T160" t="n">
         <v>36.8</v>
       </c>
-      <c r="T160" t="n">
+      <c r="U160" t="n">
         <v>30.4</v>
       </c>
-      <c r="U160" t="n">
+      <c r="V160" t="n">
         <v>52.2</v>
       </c>
-      <c r="V160" t="n">
-        <v>-1</v>
-      </c>
       <c r="W160" t="n">
-        <v>1.74459579941446</v>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>1</v>
+      </c>
+      <c r="X160" t="n">
+        <v>1.077145082286462</v>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12993,32 +13475,35 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q161" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R161" t="n">
+        <v>74</v>
+      </c>
+      <c r="S161" t="n">
         <v>30</v>
       </c>
-      <c r="S161" t="n">
+      <c r="T161" t="n">
         <v>35.8</v>
       </c>
-      <c r="T161" t="n">
+      <c r="U161" t="n">
         <v>30</v>
       </c>
-      <c r="U161" t="n">
+      <c r="V161" t="n">
         <v>52</v>
       </c>
-      <c r="V161" t="n">
-        <v>-1</v>
-      </c>
       <c r="W161" t="n">
-        <v>1.884906339691129</v>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>1</v>
+      </c>
+      <c r="X161" t="n">
+        <v>1.11119087654525</v>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13071,30 +13556,33 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>78.2</v>
+        <v>76</v>
       </c>
       <c r="Q162" t="n">
-        <v>16.78</v>
+        <v>71</v>
       </c>
       <c r="R162" t="n">
+        <v>74</v>
+      </c>
+      <c r="S162" t="n">
         <v>30</v>
       </c>
-      <c r="S162" t="n">
+      <c r="T162" t="n">
         <v>35.6</v>
       </c>
-      <c r="T162" t="n">
+      <c r="U162" t="n">
         <v>29.8</v>
       </c>
-      <c r="U162" t="n">
+      <c r="V162" t="n">
         <v>58</v>
       </c>
-      <c r="V162" t="n">
+      <c r="W162" t="n">
         <v>-1</v>
       </c>
-      <c r="W162" t="n">
-        <v>1.83017146393586</v>
-      </c>
-      <c r="X162" t="inlineStr">
+      <c r="X162" t="n">
+        <v>1.70975201179584</v>
+      </c>
+      <c r="Y162" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -13149,30 +13637,33 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>78.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q163" t="n">
-        <v>17.78</v>
+        <v>71</v>
       </c>
       <c r="R163" t="n">
+        <v>74</v>
+      </c>
+      <c r="S163" t="n">
         <v>29.8</v>
       </c>
-      <c r="S163" t="n">
+      <c r="T163" t="n">
         <v>35.4</v>
       </c>
-      <c r="T163" t="n">
+      <c r="U163" t="n">
         <v>29.4</v>
       </c>
-      <c r="U163" t="n">
+      <c r="V163" t="n">
         <v>58</v>
       </c>
-      <c r="V163" t="n">
+      <c r="W163" t="n">
         <v>-1</v>
       </c>
-      <c r="W163" t="n">
-        <v>1.829600648623321</v>
-      </c>
-      <c r="X163" t="inlineStr">
+      <c r="X163" t="n">
+        <v>1.784749131867778</v>
+      </c>
+      <c r="Y163" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -13227,30 +13718,33 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>79.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q164" t="n">
-        <v>18.26</v>
+        <v>71</v>
       </c>
       <c r="R164" t="n">
+        <v>74</v>
+      </c>
+      <c r="S164" t="n">
         <v>30.2</v>
       </c>
-      <c r="S164" t="n">
+      <c r="T164" t="n">
         <v>36</v>
       </c>
-      <c r="T164" t="n">
+      <c r="U164" t="n">
         <v>29.6</v>
       </c>
-      <c r="U164" t="n">
+      <c r="V164" t="n">
         <v>58</v>
       </c>
-      <c r="V164" t="n">
+      <c r="W164" t="n">
         <v>-1</v>
       </c>
-      <c r="W164" t="n">
-        <v>1.70050482413007</v>
-      </c>
-      <c r="X164" t="inlineStr">
+      <c r="X164" t="n">
+        <v>1.766274710563058</v>
+      </c>
+      <c r="Y164" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -13305,32 +13799,35 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>98.8</v>
+        <v>76</v>
       </c>
       <c r="Q165" t="n">
-        <v>18.78</v>
+        <v>71</v>
       </c>
       <c r="R165" t="n">
+        <v>74</v>
+      </c>
+      <c r="S165" t="n">
         <v>31.2</v>
       </c>
-      <c r="S165" t="n">
+      <c r="T165" t="n">
         <v>37</v>
       </c>
-      <c r="T165" t="n">
+      <c r="U165" t="n">
         <v>29.4</v>
       </c>
-      <c r="U165" t="n">
+      <c r="V165" t="n">
         <v>57.8</v>
       </c>
-      <c r="V165" t="n">
-        <v>1</v>
-      </c>
       <c r="W165" t="n">
-        <v>1.395493433203493</v>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>-1</v>
+      </c>
+      <c r="X165" t="n">
+        <v>1.770282743710486</v>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -13383,32 +13880,35 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>101.4</v>
+        <v>76</v>
       </c>
       <c r="Q166" t="n">
-        <v>18.68</v>
+        <v>71</v>
       </c>
       <c r="R166" t="n">
+        <v>74</v>
+      </c>
+      <c r="S166" t="n">
         <v>32.2</v>
       </c>
-      <c r="S166" t="n">
+      <c r="T166" t="n">
         <v>38</v>
       </c>
-      <c r="T166" t="n">
+      <c r="U166" t="n">
         <v>29.6</v>
       </c>
-      <c r="U166" t="n">
+      <c r="V166" t="n">
         <v>57.8</v>
       </c>
-      <c r="V166" t="n">
-        <v>1</v>
-      </c>
       <c r="W166" t="n">
-        <v>1.15181154110974</v>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X166" t="n">
+        <v>1.94876373137588</v>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -13461,30 +13961,33 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q167" t="n">
-        <v>16.92</v>
+        <v>71</v>
       </c>
       <c r="R167" t="n">
+        <v>74</v>
+      </c>
+      <c r="S167" t="n">
         <v>32.6</v>
       </c>
-      <c r="S167" t="n">
+      <c r="T167" t="n">
         <v>37.8</v>
       </c>
-      <c r="T167" t="n">
+      <c r="U167" t="n">
         <v>29.8</v>
       </c>
-      <c r="U167" t="n">
+      <c r="V167" t="n">
         <v>51.4</v>
       </c>
-      <c r="V167" t="n">
-        <v>1</v>
-      </c>
       <c r="W167" t="n">
-        <v>1.009373050965114</v>
-      </c>
-      <c r="X167" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X167" t="n">
+        <v>1.076624390176279</v>
+      </c>
+      <c r="Y167" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13539,30 +14042,33 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>102.8</v>
+        <v>76</v>
       </c>
       <c r="Q168" t="n">
-        <v>16.62</v>
+        <v>71</v>
       </c>
       <c r="R168" t="n">
+        <v>74</v>
+      </c>
+      <c r="S168" t="n">
         <v>32.2</v>
       </c>
-      <c r="S168" t="n">
+      <c r="T168" t="n">
         <v>37.8</v>
       </c>
-      <c r="T168" t="n">
+      <c r="U168" t="n">
         <v>30</v>
       </c>
-      <c r="U168" t="n">
+      <c r="V168" t="n">
         <v>50.8</v>
       </c>
-      <c r="V168" t="n">
-        <v>1</v>
-      </c>
       <c r="W168" t="n">
-        <v>1.00838229402676</v>
-      </c>
-      <c r="X168" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X168" t="n">
+        <v>1.074019574961762</v>
+      </c>
+      <c r="Y168" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13617,30 +14123,33 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>102.2</v>
+        <v>76</v>
       </c>
       <c r="Q169" t="n">
-        <v>17.52</v>
+        <v>71</v>
       </c>
       <c r="R169" t="n">
+        <v>74</v>
+      </c>
+      <c r="S169" t="n">
         <v>31.6</v>
       </c>
-      <c r="S169" t="n">
+      <c r="T169" t="n">
         <v>37.2</v>
       </c>
-      <c r="T169" t="n">
+      <c r="U169" t="n">
         <v>29.8</v>
       </c>
-      <c r="U169" t="n">
+      <c r="V169" t="n">
         <v>50.4</v>
       </c>
-      <c r="V169" t="n">
-        <v>1</v>
-      </c>
       <c r="W169" t="n">
-        <v>0.9911064263086853</v>
-      </c>
-      <c r="X169" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X169" t="n">
+        <v>1.292887663187246</v>
+      </c>
+      <c r="Y169" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13695,30 +14204,33 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q170" t="n">
-        <v>17.96</v>
+        <v>71</v>
       </c>
       <c r="R170" t="n">
+        <v>74</v>
+      </c>
+      <c r="S170" t="n">
         <v>31.6</v>
       </c>
-      <c r="S170" t="n">
+      <c r="T170" t="n">
         <v>37.8</v>
       </c>
-      <c r="T170" t="n">
+      <c r="U170" t="n">
         <v>30</v>
       </c>
-      <c r="U170" t="n">
+      <c r="V170" t="n">
         <v>50.4</v>
       </c>
-      <c r="V170" t="n">
-        <v>1</v>
-      </c>
       <c r="W170" t="n">
-        <v>0.9851399085380228</v>
-      </c>
-      <c r="X170" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X170" t="n">
+        <v>1.162399725961353</v>
+      </c>
+      <c r="Y170" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13773,30 +14285,33 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>101.2</v>
+        <v>76</v>
       </c>
       <c r="Q171" t="n">
-        <v>18.4</v>
+        <v>71</v>
       </c>
       <c r="R171" t="n">
+        <v>74</v>
+      </c>
+      <c r="S171" t="n">
         <v>31.6</v>
       </c>
-      <c r="S171" t="n">
+      <c r="T171" t="n">
         <v>38.4</v>
       </c>
-      <c r="T171" t="n">
+      <c r="U171" t="n">
         <v>30</v>
       </c>
-      <c r="U171" t="n">
+      <c r="V171" t="n">
         <v>50.4</v>
       </c>
-      <c r="V171" t="n">
-        <v>1</v>
-      </c>
       <c r="W171" t="n">
-        <v>1.011174105235851</v>
-      </c>
-      <c r="X171" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X171" t="n">
+        <v>1.099640748173494</v>
+      </c>
+      <c r="Y171" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13851,30 +14366,33 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q172" t="n">
-        <v>18.1</v>
+        <v>71</v>
       </c>
       <c r="R172" t="n">
+        <v>74</v>
+      </c>
+      <c r="S172" t="n">
         <v>31.4</v>
       </c>
-      <c r="S172" t="n">
+      <c r="T172" t="n">
         <v>38.4</v>
       </c>
-      <c r="T172" t="n">
+      <c r="U172" t="n">
         <v>30</v>
       </c>
-      <c r="U172" t="n">
+      <c r="V172" t="n">
         <v>50.8</v>
       </c>
-      <c r="V172" t="n">
-        <v>1</v>
-      </c>
       <c r="W172" t="n">
-        <v>0.9856353431794135</v>
-      </c>
-      <c r="X172" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X172" t="n">
+        <v>1.103867277178887</v>
+      </c>
+      <c r="Y172" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -13929,30 +14447,33 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>100.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q173" t="n">
-        <v>16</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R173" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S173" t="n">
         <v>40.8</v>
       </c>
-      <c r="S173" t="n">
+      <c r="T173" t="n">
         <v>46</v>
       </c>
-      <c r="T173" t="n">
+      <c r="U173" t="n">
         <v>34</v>
       </c>
-      <c r="U173" t="n">
+      <c r="V173" t="n">
         <v>66.2</v>
       </c>
-      <c r="V173" t="n">
+      <c r="W173" t="n">
         <v>-1</v>
       </c>
-      <c r="W173" t="n">
-        <v>3.067965382901833</v>
-      </c>
-      <c r="X173" t="inlineStr">
+      <c r="X173" t="n">
+        <v>3.132299162260456</v>
+      </c>
+      <c r="Y173" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -14007,30 +14528,33 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>101.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>15.14</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R174" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S174" t="n">
         <v>41.4</v>
       </c>
-      <c r="S174" t="n">
+      <c r="T174" t="n">
         <v>46</v>
       </c>
-      <c r="T174" t="n">
+      <c r="U174" t="n">
         <v>34.2</v>
       </c>
-      <c r="U174" t="n">
+      <c r="V174" t="n">
         <v>66.8</v>
       </c>
-      <c r="V174" t="n">
+      <c r="W174" t="n">
         <v>-1</v>
       </c>
-      <c r="W174" t="n">
-        <v>2.990829043866404</v>
-      </c>
-      <c r="X174" t="inlineStr">
+      <c r="X174" t="n">
+        <v>3.338168770334035</v>
+      </c>
+      <c r="Y174" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -14085,30 +14609,33 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>100.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q175" t="n">
-        <v>15.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R175" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S175" t="n">
         <v>41.6</v>
       </c>
-      <c r="S175" t="n">
+      <c r="T175" t="n">
         <v>45.4</v>
       </c>
-      <c r="T175" t="n">
+      <c r="U175" t="n">
         <v>34.4</v>
       </c>
-      <c r="U175" t="n">
+      <c r="V175" t="n">
         <v>67.2</v>
       </c>
-      <c r="V175" t="n">
+      <c r="W175" t="n">
         <v>-1</v>
       </c>
-      <c r="W175" t="n">
-        <v>2.939970939111556</v>
-      </c>
-      <c r="X175" t="inlineStr">
+      <c r="X175" t="n">
+        <v>3.428879210697342</v>
+      </c>
+      <c r="Y175" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -14163,30 +14690,33 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>100.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q176" t="n">
-        <v>15.86</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R176" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S176" t="n">
         <v>41.6</v>
       </c>
-      <c r="S176" t="n">
+      <c r="T176" t="n">
         <v>44.8</v>
       </c>
-      <c r="T176" t="n">
+      <c r="U176" t="n">
         <v>34.4</v>
       </c>
-      <c r="U176" t="n">
+      <c r="V176" t="n">
         <v>67.2</v>
       </c>
-      <c r="V176" t="n">
+      <c r="W176" t="n">
         <v>-1</v>
       </c>
-      <c r="W176" t="n">
-        <v>3.015724343397169</v>
-      </c>
-      <c r="X176" t="inlineStr">
+      <c r="X176" t="n">
+        <v>3.358995391629902</v>
+      </c>
+      <c r="Y176" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -14241,30 +14771,33 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>100.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q177" t="n">
-        <v>16.36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R177" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S177" t="n">
         <v>41.2</v>
       </c>
-      <c r="S177" t="n">
+      <c r="T177" t="n">
         <v>45.2</v>
       </c>
-      <c r="T177" t="n">
+      <c r="U177" t="n">
         <v>34.4</v>
       </c>
-      <c r="U177" t="n">
+      <c r="V177" t="n">
         <v>67.2</v>
       </c>
-      <c r="V177" t="n">
+      <c r="W177" t="n">
         <v>-1</v>
       </c>
-      <c r="W177" t="n">
-        <v>3.005401635854629</v>
-      </c>
-      <c r="X177" t="inlineStr">
+      <c r="X177" t="n">
+        <v>3.376644052294439</v>
+      </c>
+      <c r="Y177" t="inlineStr">
         <is>
           <t>Investigation Needed (Operational Drift)</t>
         </is>
@@ -14319,30 +14852,33 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>102.6</v>
+        <v>76</v>
       </c>
       <c r="Q178" t="n">
-        <v>16.76</v>
+        <v>71</v>
       </c>
       <c r="R178" t="n">
+        <v>74</v>
+      </c>
+      <c r="S178" t="n">
         <v>32</v>
       </c>
-      <c r="S178" t="n">
+      <c r="T178" t="n">
         <v>37.8</v>
       </c>
-      <c r="T178" t="n">
+      <c r="U178" t="n">
         <v>30.4</v>
       </c>
-      <c r="U178" t="n">
+      <c r="V178" t="n">
         <v>52.2</v>
       </c>
-      <c r="V178" t="n">
-        <v>1</v>
-      </c>
       <c r="W178" t="n">
-        <v>1.008972120372906</v>
-      </c>
-      <c r="X178" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X178" t="n">
+        <v>0.977442528815845</v>
+      </c>
+      <c r="Y178" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14397,30 +14933,33 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q179" t="n">
-        <v>16.96</v>
+        <v>71</v>
       </c>
       <c r="R179" t="n">
+        <v>74</v>
+      </c>
+      <c r="S179" t="n">
         <v>32</v>
       </c>
-      <c r="S179" t="n">
+      <c r="T179" t="n">
         <v>38</v>
       </c>
-      <c r="T179" t="n">
+      <c r="U179" t="n">
         <v>30.4</v>
       </c>
-      <c r="U179" t="n">
+      <c r="V179" t="n">
         <v>52.2</v>
       </c>
-      <c r="V179" t="n">
-        <v>1</v>
-      </c>
       <c r="W179" t="n">
-        <v>1.009991294583432</v>
-      </c>
-      <c r="X179" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X179" t="n">
+        <v>0.9703831882514378</v>
+      </c>
+      <c r="Y179" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14475,30 +15014,33 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q180" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R180" t="n">
+        <v>74</v>
+      </c>
+      <c r="S180" t="n">
         <v>31.8</v>
       </c>
-      <c r="S180" t="n">
+      <c r="T180" t="n">
         <v>38</v>
       </c>
-      <c r="T180" t="n">
+      <c r="U180" t="n">
         <v>30.4</v>
       </c>
-      <c r="U180" t="n">
+      <c r="V180" t="n">
         <v>52</v>
       </c>
-      <c r="V180" t="n">
-        <v>1</v>
-      </c>
       <c r="W180" t="n">
-        <v>1.009230420172821</v>
-      </c>
-      <c r="X180" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X180" t="n">
+        <v>0.9678264931896319</v>
+      </c>
+      <c r="Y180" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14553,30 +15095,33 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q181" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R181" t="n">
+        <v>74</v>
+      </c>
+      <c r="S181" t="n">
         <v>32.4</v>
       </c>
-      <c r="S181" t="n">
+      <c r="T181" t="n">
         <v>38.2</v>
       </c>
-      <c r="T181" t="n">
+      <c r="U181" t="n">
         <v>30.4</v>
       </c>
-      <c r="U181" t="n">
+      <c r="V181" t="n">
         <v>52</v>
       </c>
-      <c r="V181" t="n">
-        <v>1</v>
-      </c>
       <c r="W181" t="n">
-        <v>1.010119075364073</v>
-      </c>
-      <c r="X181" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X181" t="n">
+        <v>0.9866288240625624</v>
+      </c>
+      <c r="Y181" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14631,30 +15176,33 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q182" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R182" t="n">
+        <v>74</v>
+      </c>
+      <c r="S182" t="n">
         <v>32.8</v>
       </c>
-      <c r="S182" t="n">
+      <c r="T182" t="n">
         <v>38</v>
       </c>
-      <c r="T182" t="n">
+      <c r="U182" t="n">
         <v>30.4</v>
       </c>
-      <c r="U182" t="n">
+      <c r="V182" t="n">
         <v>51.6</v>
       </c>
-      <c r="V182" t="n">
-        <v>1</v>
-      </c>
       <c r="W182" t="n">
-        <v>1.010982416744109</v>
-      </c>
-      <c r="X182" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X182" t="n">
+        <v>0.9886068581127953</v>
+      </c>
+      <c r="Y182" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14709,30 +15257,33 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q183" t="n">
-        <v>16.78</v>
+        <v>71</v>
       </c>
       <c r="R183" t="n">
+        <v>74</v>
+      </c>
+      <c r="S183" t="n">
         <v>33.2</v>
       </c>
-      <c r="S183" t="n">
+      <c r="T183" t="n">
         <v>37.8</v>
       </c>
-      <c r="T183" t="n">
+      <c r="U183" t="n">
         <v>30.4</v>
       </c>
-      <c r="U183" t="n">
+      <c r="V183" t="n">
         <v>51.2</v>
       </c>
-      <c r="V183" t="n">
-        <v>1</v>
-      </c>
       <c r="W183" t="n">
-        <v>1.009994168089707</v>
-      </c>
-      <c r="X183" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X183" t="n">
+        <v>1.016625544785467</v>
+      </c>
+      <c r="Y183" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14787,30 +15338,33 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>103.8</v>
+        <v>76</v>
       </c>
       <c r="Q184" t="n">
-        <v>15.32</v>
+        <v>71</v>
       </c>
       <c r="R184" t="n">
+        <v>74</v>
+      </c>
+      <c r="S184" t="n">
         <v>33.4</v>
       </c>
-      <c r="S184" t="n">
+      <c r="T184" t="n">
         <v>37.2</v>
       </c>
-      <c r="T184" t="n">
+      <c r="U184" t="n">
         <v>30</v>
       </c>
-      <c r="U184" t="n">
+      <c r="V184" t="n">
         <v>50.8</v>
       </c>
-      <c r="V184" t="n">
-        <v>1</v>
-      </c>
       <c r="W184" t="n">
-        <v>1.084935730798538</v>
-      </c>
-      <c r="X184" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X184" t="n">
+        <v>1.21708223433346</v>
+      </c>
+      <c r="Y184" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14865,30 +15419,33 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="Q185" t="n">
-        <v>15.4</v>
+        <v>71</v>
       </c>
       <c r="R185" t="n">
+        <v>74</v>
+      </c>
+      <c r="S185" t="n">
         <v>32.6</v>
       </c>
-      <c r="S185" t="n">
+      <c r="T185" t="n">
         <v>36.6</v>
       </c>
-      <c r="T185" t="n">
+      <c r="U185" t="n">
         <v>30.4</v>
       </c>
-      <c r="U185" t="n">
+      <c r="V185" t="n">
         <v>52.8</v>
       </c>
-      <c r="V185" t="n">
-        <v>1</v>
-      </c>
       <c r="W185" t="n">
-        <v>1.009456168601866</v>
-      </c>
-      <c r="X185" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="X185" t="n">
+        <v>1.234263930595692</v>
+      </c>
+      <c r="Y185" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -14943,32 +15500,35 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q186" t="n">
-        <v>15.22</v>
+        <v>71</v>
       </c>
       <c r="R186" t="n">
+        <v>74</v>
+      </c>
+      <c r="S186" t="n">
         <v>32.2</v>
       </c>
-      <c r="S186" t="n">
+      <c r="T186" t="n">
         <v>36.2</v>
       </c>
-      <c r="T186" t="n">
+      <c r="U186" t="n">
         <v>30.8</v>
       </c>
-      <c r="U186" t="n">
+      <c r="V186" t="n">
         <v>54.8</v>
       </c>
-      <c r="V186" t="n">
-        <v>1</v>
-      </c>
       <c r="W186" t="n">
-        <v>1.08967145102651</v>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X186" t="n">
+        <v>1.404957282447552</v>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -15021,32 +15581,35 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q187" t="n">
-        <v>15.14</v>
+        <v>71</v>
       </c>
       <c r="R187" t="n">
+        <v>74</v>
+      </c>
+      <c r="S187" t="n">
         <v>31.8</v>
       </c>
-      <c r="S187" t="n">
+      <c r="T187" t="n">
         <v>36.2</v>
       </c>
-      <c r="T187" t="n">
+      <c r="U187" t="n">
         <v>30.8</v>
       </c>
-      <c r="U187" t="n">
+      <c r="V187" t="n">
         <v>56.4</v>
       </c>
-      <c r="V187" t="n">
-        <v>1</v>
-      </c>
       <c r="W187" t="n">
-        <v>1.170908098120478</v>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X187" t="n">
+        <v>1.442162852226416</v>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -15099,32 +15662,35 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>93.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q188" t="n">
-        <v>15.02</v>
+        <v>70.8</v>
       </c>
       <c r="R188" t="n">
+        <v>74</v>
+      </c>
+      <c r="S188" t="n">
         <v>32.2</v>
       </c>
-      <c r="S188" t="n">
+      <c r="T188" t="n">
         <v>35.8</v>
       </c>
-      <c r="T188" t="n">
+      <c r="U188" t="n">
         <v>31</v>
       </c>
-      <c r="U188" t="n">
+      <c r="V188" t="n">
         <v>57.6</v>
       </c>
-      <c r="V188" t="n">
-        <v>1</v>
-      </c>
       <c r="W188" t="n">
-        <v>1.253438344915729</v>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>1</v>
+      </c>
+      <c r="X188" t="n">
+        <v>1.598547847865989</v>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -15177,32 +15743,35 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q189" t="n">
-        <v>14.78</v>
+        <v>70.8</v>
       </c>
       <c r="R189" t="n">
+        <v>74</v>
+      </c>
+      <c r="S189" t="n">
         <v>32.4</v>
       </c>
-      <c r="S189" t="n">
+      <c r="T189" t="n">
         <v>36</v>
       </c>
-      <c r="T189" t="n">
+      <c r="U189" t="n">
         <v>31.2</v>
       </c>
-      <c r="U189" t="n">
+      <c r="V189" t="n">
         <v>59</v>
       </c>
-      <c r="V189" t="n">
-        <v>1</v>
-      </c>
       <c r="W189" t="n">
-        <v>1.396692262845437</v>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>-1</v>
+      </c>
+      <c r="X189" t="n">
+        <v>1.767088331571478</v>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -15255,32 +15824,35 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q190" t="n">
-        <v>14.34</v>
+        <v>70.8</v>
       </c>
       <c r="R190" t="n">
+        <v>74</v>
+      </c>
+      <c r="S190" t="n">
         <v>33.8</v>
       </c>
-      <c r="S190" t="n">
+      <c r="T190" t="n">
         <v>36.2</v>
       </c>
-      <c r="T190" t="n">
+      <c r="U190" t="n">
         <v>30.6</v>
       </c>
-      <c r="U190" t="n">
+      <c r="V190" t="n">
         <v>58.2</v>
       </c>
-      <c r="V190" t="n">
-        <v>1</v>
-      </c>
       <c r="W190" t="n">
-        <v>1.462818915464896</v>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>-1</v>
+      </c>
+      <c r="X190" t="n">
+        <v>1.762558480458336</v>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -15333,32 +15905,35 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>91.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q191" t="n">
-        <v>15.92</v>
+        <v>70.8</v>
       </c>
       <c r="R191" t="n">
+        <v>74</v>
+      </c>
+      <c r="S191" t="n">
         <v>33.8</v>
       </c>
-      <c r="S191" t="n">
+      <c r="T191" t="n">
         <v>36.4</v>
       </c>
-      <c r="T191" t="n">
+      <c r="U191" t="n">
         <v>30.6</v>
       </c>
-      <c r="U191" t="n">
+      <c r="V191" t="n">
         <v>58</v>
       </c>
-      <c r="V191" t="n">
-        <v>1</v>
-      </c>
       <c r="W191" t="n">
-        <v>1.272162930419183</v>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>-1</v>
+      </c>
+      <c r="X191" t="n">
+        <v>1.724935965103277</v>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
